--- a/StructureDefinition-mii-pr-pro-questionnaire-response.xlsx
+++ b/StructureDefinition-mii-pr-pro-questionnaire-response.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AL$44</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AL$65</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1538" uniqueCount="320">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2245" uniqueCount="399">
   <si>
     <t>Property</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2027.0.0-ballot.rc3</t>
+    <t>2027.0.0-ballot.rc4</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-07T17:47:08+00:00</t>
+    <t>2026-09-08T17:30:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -260,7 +260,7 @@
 </t>
   </si>
   <si>
-    <t>SDC Questionnaire Response</t>
+    <t>Standard Questionnaire Response</t>
   </si>
   <si>
     <t>Sets expectations for supported capabilities for questionnaire responses for SDC-conformant systems.</t>
@@ -270,7 +270,7 @@
   </si>
   <si>
     <t>dom-2:If the resource is contained in another resource, it SHALL NOT contain nested Resources {contained.contained.empty()}
-dom-3:If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where((('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(canonical) = '#').exists()).not()).trace('unmatched', id).empty()}dom-4:If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-5:If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}dom-6:A resource should have narrative for robust management {text.`div`.exists()}sdcqr-1:Subject SHOULD be present (searching is difficult without subject).  Almost all QuestionnaireResponses should be with respect to some sort of subject. {subject.exists()}sdcqr-2:When repeats=true for a group, it'll be represented with multiple items with the same linkId in the QuestionnaireResponse.  For a question, it'll be represented by a single item with that linkId with multiple answers. {(QuestionnaireResponse|repeat(answer|item)).select(item.where(answer.value.exists()).linkId.isDistinct()).allTrue()}</t>
+dom-3:If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where((('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(canonical) = '#').exists()).not()).trace('unmatched', id).empty()}dom-4:If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-5:If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}dom-6:A resource should have narrative for robust management {text.`div`.exists()}sdcqr-1:Subject SHOULD be present (searching is difficult without subject).  Almost all QuestionnaireResponses should be with respect to some sort of subject. {subject.exists()}sdcqr-2:When repeats=true for a group, it'll be represented with multiple items with the same linkId in the QuestionnaireResponse.  For a question, it'll be represented by a single item with that linkId with multiple answers. {(QuestionnaireResponse|repeat(answer|item)).select(item.where(answer.value.exists()).linkId.isDistinct()).allTrue()}sdcqr-3:Can either have source or source extension, but not both {source.count() + extension.where(url='http://hl7.org/fhir/5.0/StructureDefinition/extension-QuestionnaireResponse.source').count() &lt;=1}</t>
   </si>
   <si>
     <t>Event</t>
@@ -441,33 +441,158 @@
 ext-1:Must have either extensions or value[x], not both {extension.exists() != value.exists()}</t>
   </si>
   <si>
-    <t>QuestionnaireResponse.extension:signature</t>
-  </si>
-  <si>
-    <t>signature</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Extension {questionnaireresponse-signature}
+    <t>QuestionnaireResponse.extension:adheresTo</t>
+  </si>
+  <si>
+    <t>adheresTo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extension {workflow-adheresTo|5.3.0-ballot-tc1}
 </t>
   </si>
   <si>
-    <t>A signature attesting to the content</t>
-  </si>
-  <si>
-    <t>Represents a wet or electronic signature for either the form overall or for the question or item it's associated with.</t>
+    <t>Follows rules from</t>
+  </si>
+  <si>
+    <t>The action represented by this resource has been determined to satisfy the expectations established by the referenced Definition resource.</t>
+  </si>
+  <si>
+    <t>If changes are made to this event record, the determination must be made whether, with the change, the action still complies with the referenced Definition.  Revisions may result in adheresTo assertions being removed, or - if the system has an algorithm for determining which targets are appropriate - being added.  Adherence may be asserted after the fact.  It is possible for a Request or Event to adhere to a Definition even if the author/performer of the action was not aware of the Definition at the time the action was taken/requested.
+Also see the [notes](http://hl7.org/fhir/R4/workflow-extensions.html#instantiation) in the workflow extensions area for more guidance on this element.</t>
   </si>
   <si>
     <t xml:space="preserve">ele-1
 </t>
   </si>
   <si>
+    <t>QuestionnaireResponse.extension:adheresTo.id</t>
+  </si>
+  <si>
+    <t>QuestionnaireResponse.extension.id</t>
+  </si>
+  <si>
+    <t xml:space="preserve">string
+</t>
+  </si>
+  <si>
+    <t>Unique id for inter-element referencing</t>
+  </si>
+  <si>
+    <t>Unique id for the element within a resource (for internal references). This may be any string value that does not contain spaces.</t>
+  </si>
+  <si>
+    <t>Element.id</t>
+  </si>
+  <si>
+    <t>QuestionnaireResponse.extension:adheresTo.extension</t>
+  </si>
+  <si>
+    <t>QuestionnaireResponse.extension.extension</t>
+  </si>
+  <si>
+    <t>Extensions are always sliced by (at least) url</t>
+  </si>
+  <si>
+    <t>Element.extension</t>
+  </si>
+  <si>
+    <t>QuestionnaireResponse.extension:adheresTo.url</t>
+  </si>
+  <si>
+    <t>QuestionnaireResponse.extension.url</t>
+  </si>
+  <si>
+    <t>identifies the meaning of the extension</t>
+  </si>
+  <si>
+    <t>Source of the definition for the extension code - a logical name or a URL.</t>
+  </si>
+  <si>
+    <t>The definition may point directly to a computable or human-readable definition of the extensibility codes, or it may be a logical URI as declared in some other specification. The definition SHALL be a URI for the Structure Definition defining the extension.</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/StructureDefinition/workflow-adheresTo</t>
+  </si>
+  <si>
+    <t>Extension.url</t>
+  </si>
+  <si>
+    <t>QuestionnaireResponse.extension:adheresTo.value[x]</t>
+  </si>
+  <si>
+    <t>QuestionnaireResponse.extension.value[x]</t>
+  </si>
+  <si>
+    <t>canonical(ActivityDefinition|PlanDefinition)
+Reference(ActivityDefinition|PlanDefinition)uri</t>
+  </si>
+  <si>
+    <t>Value of extension</t>
+  </si>
+  <si>
+    <t>Value of extension - must be one of a constrained set of the data types (see [Extensibility](http://hl7.org/fhir/R4/extensibility.html) for a list).</t>
+  </si>
+  <si>
+    <t>Extension.value[x]</t>
+  </si>
+  <si>
+    <t>QuestionnaireResponse.extension:triggeredBy</t>
+  </si>
+  <si>
+    <t>triggeredBy</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extension {workflow-triggeredBy|5.3.0-ballot-tc1}
+</t>
+  </si>
+  <si>
+    <t>Created because of following</t>
+  </si>
+  <si>
+    <t>This resource came into being as a result of expectations set in the referenced Definition resource.  I.e. This resource represents a 'step' dictated within the protocol/order set/etc.</t>
+  </si>
+  <si>
+    <t>See the [notes](http://hl7.org/fhir/R4/workflow-extensions.html#instantiation) in the workflow extensions area for more guidance on this element.</t>
+  </si>
+  <si>
+    <t>QuestionnaireResponse.extension:triggeredBy.id</t>
+  </si>
+  <si>
+    <t>QuestionnaireResponse.extension:triggeredBy.extension</t>
+  </si>
+  <si>
+    <t>QuestionnaireResponse.extension:triggeredBy.url</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/StructureDefinition/workflow-triggeredBy</t>
+  </si>
+  <si>
+    <t>QuestionnaireResponse.extension:triggeredBy.value[x]</t>
+  </si>
+  <si>
+    <t>QuestionnaireResponse.extension:signature</t>
+  </si>
+  <si>
+    <t>signature</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extension {questionnaireresponse-signature|5.3.0-ballot-tc1}
+</t>
+  </si>
+  <si>
+    <t>A signature attesting to the content</t>
+  </si>
+  <si>
+    <t>Represents a wet or electronic signature for either the form overall or for the question or item it's associated with.</t>
+  </si>
+  <si>
     <t>QuestionnaireResponse.extension:completionMode</t>
   </si>
   <si>
     <t>completionMode</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {questionnaireresponse-completionMode}
+    <t xml:space="preserve">Extension {questionnaireresponse-completionMode|5.3.0-ballot-tc1}
 </t>
   </si>
   <si>
@@ -593,32 +718,22 @@
     <t>QuestionnaireResponse.questionnaire.id</t>
   </si>
   <si>
-    <t xml:space="preserve">string
-</t>
-  </si>
-  <si>
     <t>xml:id (or equivalent in JSON)</t>
   </si>
   <si>
     <t>unique id for the element within a resource (for internal references)</t>
   </si>
   <si>
-    <t>Element.id</t>
-  </si>
-  <si>
     <t>QuestionnaireResponse.questionnaire.extension</t>
   </si>
   <si>
-    <t>Element.extension</t>
-  </si>
-  <si>
     <t>QuestionnaireResponse.questionnaire.extension:questionnaireDisplay</t>
   </si>
   <si>
     <t>questionnaireDisplay</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {display}
+    <t xml:space="preserve">Extension {display|5.3.0-ballot-tc1}
 </t>
   </si>
   <si>
@@ -806,6 +921,145 @@
     <t>FiveWs.source</t>
   </si>
   <si>
+    <t>QuestionnaireResponse.source.id</t>
+  </si>
+  <si>
+    <t>QuestionnaireResponse.source.extension</t>
+  </si>
+  <si>
+    <t>Additional content defined by implementations</t>
+  </si>
+  <si>
+    <t>May be used to represent additional information that is not part of the basic definition of the element. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
+  </si>
+  <si>
+    <t>QuestionnaireResponse.source.extension:r5Source</t>
+  </si>
+  <si>
+    <t>r5Source</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extension {alternate-reference|5.3.0-ballot-tc1}
+</t>
+  </si>
+  <si>
+    <t>Alternative reference (target type is wrong)</t>
+  </si>
+  <si>
+    <t>Used when the target of the reference has a type that is not allowed by the definition of the element. In general, this should only arise when wrangling between versions using cross-version extensions.</t>
+  </si>
+  <si>
+    <t>Given that a reference SHALL have a display or reference, using this extension implies that there's a display present.</t>
+  </si>
+  <si>
+    <t>QuestionnaireResponse.source.extension:r5Source.id</t>
+  </si>
+  <si>
+    <t>QuestionnaireResponse.source.extension.id</t>
+  </si>
+  <si>
+    <t>QuestionnaireResponse.source.extension:r5Source.extension</t>
+  </si>
+  <si>
+    <t>QuestionnaireResponse.source.extension.extension</t>
+  </si>
+  <si>
+    <t>QuestionnaireResponse.source.extension:r5Source.url</t>
+  </si>
+  <si>
+    <t>QuestionnaireResponse.source.extension.url</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/StructureDefinition/alternate-reference</t>
+  </si>
+  <si>
+    <t>QuestionnaireResponse.source.extension:r5Source.value[x]</t>
+  </si>
+  <si>
+    <t>QuestionnaireResponse.source.extension.value[x]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reference(Device|Organization)
+</t>
+  </si>
+  <si>
+    <t>QuestionnaireResponse.source.reference</t>
+  </si>
+  <si>
+    <t>Literal reference, Relative, internal or absolute URL</t>
+  </si>
+  <si>
+    <t>A reference to a location at which the other resource is found. The reference may be a relative reference, in which case it is relative to the service base URL, or an absolute URL that resolves to the location where the resource is found. The reference may be version specific or not. If the reference is not to a FHIR RESTful server, then it should be assumed to be version specific. Internal fragment references (start with '#') refer to contained resources.</t>
+  </si>
+  <si>
+    <t>Using absolute URLs provides a stable scalable approach suitable for a cloud/web context, while using relative/logical references provides a flexible approach suitable for use when trading across closed eco-system boundaries.   Absolute URLs do not need to point to a FHIR RESTful server, though this is the preferred approach. If the URL conforms to the structure "/[type]/[id]" then it should be assumed that the reference is to a FHIR RESTful server.</t>
+  </si>
+  <si>
+    <t>Reference.reference</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ref-1
+</t>
+  </si>
+  <si>
+    <t>QuestionnaireResponse.source.type</t>
+  </si>
+  <si>
+    <t>Type the reference refers to (e.g. "Patient")</t>
+  </si>
+  <si>
+    <t>The expected type of the target of the reference. If both Reference.type and Reference.reference are populated and Reference.reference is a FHIR URL, both SHALL be consistent.
+The type is the Canonical URL of Resource Definition that is the type this reference refers to. References are URLs that are relative to http://hl7.org/fhir/StructureDefinition/ e.g. "Patient" is a reference to http://hl7.org/fhir/StructureDefinition/Patient. Absolute URLs are only allowed for logical models (and can only be used in references in logical models, not resources).</t>
+  </si>
+  <si>
+    <t>This element is used to indicate the type of  the target of the reference. This may be used which ever of the other elements are populated (or not). In some cases, the type of the target may be determined by inspection of the reference (e.g. a RESTful URL) or by resolving the target of the reference; if both the type and a reference is provided, the reference SHALL resolve to a resource of the same type as that specified.</t>
+  </si>
+  <si>
+    <t>extensible</t>
+  </si>
+  <si>
+    <t>Aa resource (or, for logical models, the URI of the logical model).</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/resource-types|4.0.1</t>
+  </si>
+  <si>
+    <t>Reference.type</t>
+  </si>
+  <si>
+    <t>QuestionnaireResponse.source.identifier</t>
+  </si>
+  <si>
+    <t>Logical reference, when literal reference is not known</t>
+  </si>
+  <si>
+    <t>An identifier for the target resource. This is used when there is no way to reference the other resource directly, either because the entity it represents is not available through a FHIR server, or because there is no way for the author of the resource to convert a known identifier to an actual location. There is no requirement that a Reference.identifier point to something that is actually exposed as a FHIR instance, but it SHALL point to a business concept that would be expected to be exposed as a FHIR instance, and that instance would need to be of a FHIR resource type allowed by the reference.</t>
+  </si>
+  <si>
+    <t>When an identifier is provided in place of a reference, any system processing the reference will only be able to resolve the identifier to a reference if it understands the business context in which the identifier is used. Sometimes this is global (e.g. a national identifier) but often it is not. For this reason, none of the useful mechanisms described for working with references (e.g. chaining, includes) are possible, nor should servers be expected to be able resolve the reference. Servers may accept an identifier based reference untouched, resolve it, and/or reject it - see CapabilityStatement.rest.resource.referencePolicy. 
+When both an identifier and a literal reference are provided, the literal reference is preferred. Applications processing the resource are allowed - but not required - to check that the identifier matches the literal reference
+Applications converting a logical reference to a literal reference may choose to leave the logical reference present, or remove it.
+Reference is intended to point to a structure that can potentially be expressed as a FHIR resource, though there is no need for it to exist as an actual FHIR resource instance - except in as much as an application wishes to actual find the target of the reference. The content referred to be the identifier must meet the logical constraints implied by any limitations on what resource types are permitted for the reference.  For example, it would not be legitimate to send the identifier for a drug prescription if the type were Reference(Observation|DiagnosticReport).  One of the use-cases for Reference.identifier is the situation where no FHIR representation exists (where the type is Reference (Any).</t>
+  </si>
+  <si>
+    <t>Reference.identifier</t>
+  </si>
+  <si>
+    <t>QuestionnaireResponse.source.display</t>
+  </si>
+  <si>
+    <t>Text alternative for the resource</t>
+  </si>
+  <si>
+    <t>Plain text narrative that identifies the resource in addition to the resource reference.</t>
+  </si>
+  <si>
+    <t>This is generally not the same as the Resource.text of the referenced resource.  The purpose is to identify what's being referenced, not to fully describe it.</t>
+  </si>
+  <si>
+    <t>Reference.display</t>
+  </si>
+  <si>
     <t>QuestionnaireResponse.item</t>
   </si>
   <si>
@@ -823,16 +1077,10 @@
   </si>
   <si>
     <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-qrs-1:Nested item can't be beneath both item and answer {(answer.exists() and item.exists()).not()}</t>
+qrs-1:Nested item can't be beneath both item and answer {(answer.exists() and item.exists()).not()}qrs-2:Repeated answers are combined in the answers array of a single item {repeat(answer|item).select(item.where(answer.value.exists()).linkId.isDistinct()).allTrue()}</t>
   </si>
   <si>
     <t>QuestionnaireResponse.item.id</t>
-  </si>
-  <si>
-    <t>Unique id for inter-element referencing</t>
-  </si>
-  <si>
-    <t>Unique id for the element within a resource (for internal references). This may be any string value that does not contain spaces.</t>
   </si>
   <si>
     <t>QuestionnaireResponse.item.extension</t>
@@ -951,25 +1199,23 @@
     <t>Media to render/make available as an accompaniment to a specific answer option</t>
   </si>
   <si>
-    <t>QuestionnaireResponse.item.answer.extension:ordinalValue</t>
-  </si>
-  <si>
-    <t>ordinalValue</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Extension {ordinalValue}
+    <t>QuestionnaireResponse.item.answer.extension:itemWeight</t>
+  </si>
+  <si>
+    <t>itemWeight</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extension {itemWeight|5.3.0-ballot-tc1}
 </t>
   </si>
   <si>
     <t>Assigned Ordinal Value</t>
   </si>
   <si>
-    <t>A numeric value that allows the comparison (less than, greater than) or other numerical 
-manipulation of a concept (e.g. Adding up components of a score). Scores are usually a whole number, but occasionally decimals are encountered in scores.</t>
-  </si>
-  <si>
-    <t>Scores are commonly encountered in various clinical assessment scales. Assigning a value to a concept should generally be done in a formal code system that defines the value, or in an applicable value set for the concept, but some concepts do not have a formal definition (or are not even represented as a concept formally, especially in [Questionnaires](http://hl7.org/fhir/R4/questionnaire.html), 
-so this extension is allowed to appear ouside those preferred contexts.  Scores may even be assigned arbitrarily during use (hence, on Coding). The value may be constrained to an integer in some contexts of use. Todo: Scoring algorithms may also be defined directly, but how this is done is not yet defined.</t>
+    <t>A numeric value that allows the comparison (less than, greater than) or other numerical manipulation of a concept (e.g. Adding up components of a score). Scores are usually a whole number, but occasionally decimals are encountered in scores. In the CodeSystem and ValueSet resources, the item weight is represented using the [itemWeight property](http://hl7.org/fhir/R4/codesystem-concept-properties.html#concept-properties-itemWeight). In questionnaires, this extension goes on answerOption where possible.</t>
+  </si>
+  <si>
+    <t>Inclusion of weights in QRs can increase performance when calculating based on weights.</t>
   </si>
   <si>
     <t>QuestionnaireResponse.item.answer.modifierExtension</t>
@@ -979,7 +1225,7 @@
   </si>
   <si>
     <t>boolean
-datedateTimetimedecimalintegerstringCodinguriQuantityAttachmentReference</t>
+decimalintegerdatedateTimetimestringuriAttachmentCodingQuantityReference(Resource|4.0.1)</t>
   </si>
   <si>
     <t>Single-valued answer to the question</t>
@@ -1341,7 +1587,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AL44"/>
+  <dimension ref="A1:AL65"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="56.1640625" customWidth="true" bestFit="true"/>
@@ -1368,11 +1614,11 @@
     <col min="22" max="22" width="15.13671875" customWidth="true" bestFit="true"/>
     <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
-    <col min="25" max="25" width="43.26171875" customWidth="true" bestFit="true"/>
+    <col min="25" max="25" width="51.97265625" customWidth="true" bestFit="true"/>
     <col min="26" max="26" width="50.27734375" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
-    <col min="29" max="29" width="17.65625" customWidth="true" bestFit="true"/>
+    <col min="29" max="29" width="36.0390625" customWidth="true" bestFit="true"/>
     <col min="30" max="30" width="14.7578125" customWidth="true" bestFit="true"/>
     <col min="31" max="31" width="12.359375" customWidth="true" bestFit="true" hidden="true"/>
     <col min="32" max="32" width="36.73046875" customWidth="true" bestFit="true" hidden="true"/>
@@ -2395,7 +2641,9 @@
       <c r="M10" t="s" s="2">
         <v>140</v>
       </c>
-      <c r="N10" s="2"/>
+      <c r="N10" t="s" s="2">
+        <v>141</v>
+      </c>
       <c r="O10" s="2"/>
       <c r="P10" t="s" s="2">
         <v>78</v>
@@ -2453,7 +2701,7 @@
         <v>77</v>
       </c>
       <c r="AI10" t="s" s="2">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="AJ10" t="s" s="2">
         <v>135</v>
@@ -2467,14 +2715,12 @@
     </row>
     <row r="11" hidden="true">
       <c r="A11" t="s" s="2">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>128</v>
-      </c>
-      <c r="C11" t="s" s="2">
-        <v>143</v>
-      </c>
+        <v>144</v>
+      </c>
+      <c r="C11" s="2"/>
       <c r="D11" t="s" s="2">
         <v>78</v>
       </c>
@@ -2495,13 +2741,13 @@
         <v>78</v>
       </c>
       <c r="K11" t="s" s="2">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="L11" t="s" s="2">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="M11" t="s" s="2">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="N11" s="2"/>
       <c r="O11" s="2"/>
@@ -2552,19 +2798,19 @@
         <v>78</v>
       </c>
       <c r="AF11" t="s" s="2">
-        <v>134</v>
+        <v>148</v>
       </c>
       <c r="AG11" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH11" t="s" s="2">
-        <v>77</v>
+        <v>86</v>
       </c>
       <c r="AI11" t="s" s="2">
-        <v>141</v>
+        <v>78</v>
       </c>
       <c r="AJ11" t="s" s="2">
-        <v>135</v>
+        <v>78</v>
       </c>
       <c r="AK11" t="s" s="2">
         <v>78</v>
@@ -2575,27 +2821,27 @@
     </row>
     <row r="12" hidden="true">
       <c r="A12" t="s" s="2">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" t="s" s="2">
-        <v>148</v>
+        <v>78</v>
       </c>
       <c r="E12" s="2"/>
       <c r="F12" t="s" s="2">
         <v>76</v>
       </c>
       <c r="G12" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="H12" t="s" s="2">
         <v>78</v>
       </c>
       <c r="I12" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="J12" t="s" s="2">
         <v>78</v>
@@ -2604,17 +2850,13 @@
         <v>129</v>
       </c>
       <c r="L12" t="s" s="2">
-        <v>149</v>
+        <v>130</v>
       </c>
       <c r="M12" t="s" s="2">
-        <v>150</v>
-      </c>
-      <c r="N12" t="s" s="2">
-        <v>151</v>
-      </c>
-      <c r="O12" t="s" s="2">
-        <v>152</v>
-      </c>
+        <v>131</v>
+      </c>
+      <c r="N12" s="2"/>
+      <c r="O12" s="2"/>
       <c r="P12" t="s" s="2">
         <v>78</v>
       </c>
@@ -2650,19 +2892,19 @@
         <v>78</v>
       </c>
       <c r="AB12" t="s" s="2">
-        <v>78</v>
+        <v>132</v>
       </c>
       <c r="AC12" t="s" s="2">
-        <v>78</v>
+        <v>151</v>
       </c>
       <c r="AD12" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE12" t="s" s="2">
-        <v>78</v>
+        <v>133</v>
       </c>
       <c r="AF12" t="s" s="2">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="AG12" t="s" s="2">
         <v>76</v>
@@ -2683,9 +2925,9 @@
         <v>78</v>
       </c>
     </row>
-    <row r="13">
+    <row r="13" hidden="true">
       <c r="A13" t="s" s="2">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="B13" t="s" s="2">
         <v>154</v>
@@ -2696,39 +2938,39 @@
       </c>
       <c r="E13" s="2"/>
       <c r="F13" t="s" s="2">
-        <v>76</v>
+        <v>86</v>
       </c>
       <c r="G13" t="s" s="2">
         <v>86</v>
       </c>
       <c r="H13" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="I13" t="s" s="2">
         <v>78</v>
       </c>
       <c r="J13" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="K13" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="L13" t="s" s="2">
         <v>155</v>
       </c>
-      <c r="L13" t="s" s="2">
+      <c r="M13" t="s" s="2">
         <v>156</v>
       </c>
-      <c r="M13" t="s" s="2">
+      <c r="N13" t="s" s="2">
         <v>157</v>
       </c>
-      <c r="N13" s="2"/>
-      <c r="O13" t="s" s="2">
-        <v>158</v>
-      </c>
+      <c r="O13" s="2"/>
       <c r="P13" t="s" s="2">
         <v>78</v>
       </c>
       <c r="Q13" s="2"/>
       <c r="R13" t="s" s="2">
-        <v>78</v>
+        <v>158</v>
       </c>
       <c r="S13" t="s" s="2">
         <v>78</v>
@@ -2770,10 +3012,10 @@
         <v>78</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>154</v>
+        <v>159</v>
       </c>
       <c r="AG13" t="s" s="2">
-        <v>76</v>
+        <v>86</v>
       </c>
       <c r="AH13" t="s" s="2">
         <v>86</v>
@@ -2782,32 +3024,32 @@
         <v>78</v>
       </c>
       <c r="AJ13" t="s" s="2">
-        <v>98</v>
+        <v>78</v>
       </c>
       <c r="AK13" t="s" s="2">
-        <v>159</v>
+        <v>78</v>
       </c>
       <c r="AL13" t="s" s="2">
-        <v>160</v>
+        <v>78</v>
       </c>
     </row>
     <row r="14" hidden="true">
       <c r="A14" t="s" s="2">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="B14" t="s" s="2">
         <v>161</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
-        <v>162</v>
+        <v>78</v>
       </c>
       <c r="E14" s="2"/>
       <c r="F14" t="s" s="2">
-        <v>76</v>
+        <v>86</v>
       </c>
       <c r="G14" t="s" s="2">
-        <v>77</v>
+        <v>86</v>
       </c>
       <c r="H14" t="s" s="2">
         <v>78</v>
@@ -2816,21 +3058,19 @@
         <v>78</v>
       </c>
       <c r="J14" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="K14" t="s" s="2">
+        <v>162</v>
+      </c>
+      <c r="L14" t="s" s="2">
         <v>163</v>
       </c>
-      <c r="L14" t="s" s="2">
+      <c r="M14" t="s" s="2">
         <v>164</v>
       </c>
-      <c r="M14" t="s" s="2">
-        <v>165</v>
-      </c>
       <c r="N14" s="2"/>
-      <c r="O14" t="s" s="2">
-        <v>166</v>
-      </c>
+      <c r="O14" s="2"/>
       <c r="P14" t="s" s="2">
         <v>78</v>
       </c>
@@ -2878,13 +3118,13 @@
         <v>78</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>161</v>
+        <v>165</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH14" t="s" s="2">
-        <v>77</v>
+        <v>86</v>
       </c>
       <c r="AI14" t="s" s="2">
         <v>78</v>
@@ -2893,7 +3133,7 @@
         <v>98</v>
       </c>
       <c r="AK14" t="s" s="2">
-        <v>167</v>
+        <v>78</v>
       </c>
       <c r="AL14" t="s" s="2">
         <v>78</v>
@@ -2901,12 +3141,14 @@
     </row>
     <row r="15" hidden="true">
       <c r="A15" t="s" s="2">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>168</v>
-      </c>
-      <c r="C15" s="2"/>
+        <v>128</v>
+      </c>
+      <c r="C15" t="s" s="2">
+        <v>167</v>
+      </c>
       <c r="D15" t="s" s="2">
         <v>78</v>
       </c>
@@ -2915,7 +3157,7 @@
         <v>76</v>
       </c>
       <c r="G15" t="s" s="2">
-        <v>77</v>
+        <v>86</v>
       </c>
       <c r="H15" t="s" s="2">
         <v>78</v>
@@ -2924,19 +3166,19 @@
         <v>78</v>
       </c>
       <c r="J15" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="K15" t="s" s="2">
+        <v>168</v>
+      </c>
+      <c r="L15" t="s" s="2">
         <v>169</v>
       </c>
-      <c r="L15" t="s" s="2">
+      <c r="M15" t="s" s="2">
         <v>170</v>
       </c>
-      <c r="M15" t="s" s="2">
+      <c r="N15" t="s" s="2">
         <v>171</v>
-      </c>
-      <c r="N15" t="s" s="2">
-        <v>172</v>
       </c>
       <c r="O15" s="2"/>
       <c r="P15" t="s" s="2">
@@ -2986,7 +3228,7 @@
         <v>78</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>168</v>
+        <v>134</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>76</v>
@@ -2995,60 +3237,56 @@
         <v>77</v>
       </c>
       <c r="AI15" t="s" s="2">
-        <v>78</v>
+        <v>142</v>
       </c>
       <c r="AJ15" t="s" s="2">
-        <v>98</v>
+        <v>135</v>
       </c>
       <c r="AK15" t="s" s="2">
-        <v>173</v>
+        <v>78</v>
       </c>
       <c r="AL15" t="s" s="2">
         <v>78</v>
       </c>
     </row>
-    <row r="16">
+    <row r="16" hidden="true">
       <c r="A16" t="s" s="2">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>174</v>
+        <v>144</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
-        <v>175</v>
+        <v>78</v>
       </c>
       <c r="E16" s="2"/>
       <c r="F16" t="s" s="2">
-        <v>86</v>
+        <v>76</v>
       </c>
       <c r="G16" t="s" s="2">
         <v>86</v>
       </c>
       <c r="H16" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="I16" t="s" s="2">
         <v>78</v>
       </c>
       <c r="J16" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>176</v>
+        <v>145</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>177</v>
+        <v>146</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>178</v>
-      </c>
-      <c r="N16" t="s" s="2">
-        <v>179</v>
-      </c>
-      <c r="O16" t="s" s="2">
-        <v>180</v>
-      </c>
+        <v>147</v>
+      </c>
+      <c r="N16" s="2"/>
+      <c r="O16" s="2"/>
       <c r="P16" t="s" s="2">
         <v>78</v>
       </c>
@@ -3096,7 +3334,7 @@
         <v>78</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>174</v>
+        <v>148</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>76</v>
@@ -3108,10 +3346,10 @@
         <v>78</v>
       </c>
       <c r="AJ16" t="s" s="2">
-        <v>98</v>
+        <v>78</v>
       </c>
       <c r="AK16" t="s" s="2">
-        <v>181</v>
+        <v>78</v>
       </c>
       <c r="AL16" t="s" s="2">
         <v>78</v>
@@ -3119,10 +3357,10 @@
     </row>
     <row r="17" hidden="true">
       <c r="A17" t="s" s="2">
-        <v>182</v>
+        <v>173</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>182</v>
+        <v>150</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -3133,7 +3371,7 @@
         <v>76</v>
       </c>
       <c r="G17" t="s" s="2">
-        <v>86</v>
+        <v>76</v>
       </c>
       <c r="H17" t="s" s="2">
         <v>78</v>
@@ -3145,13 +3383,13 @@
         <v>78</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>183</v>
+        <v>129</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>184</v>
+        <v>130</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>185</v>
+        <v>131</v>
       </c>
       <c r="N17" s="2"/>
       <c r="O17" s="2"/>
@@ -3190,31 +3428,31 @@
         <v>78</v>
       </c>
       <c r="AB17" t="s" s="2">
-        <v>78</v>
+        <v>132</v>
       </c>
       <c r="AC17" t="s" s="2">
-        <v>78</v>
+        <v>151</v>
       </c>
       <c r="AD17" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE17" t="s" s="2">
-        <v>78</v>
+        <v>133</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>186</v>
+        <v>152</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH17" t="s" s="2">
-        <v>86</v>
+        <v>77</v>
       </c>
       <c r="AI17" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ17" t="s" s="2">
-        <v>78</v>
+        <v>135</v>
       </c>
       <c r="AK17" t="s" s="2">
         <v>78</v>
@@ -3225,10 +3463,10 @@
     </row>
     <row r="18" hidden="true">
       <c r="A18" t="s" s="2">
-        <v>187</v>
+        <v>174</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>187</v>
+        <v>154</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -3236,10 +3474,10 @@
       </c>
       <c r="E18" s="2"/>
       <c r="F18" t="s" s="2">
-        <v>76</v>
+        <v>86</v>
       </c>
       <c r="G18" t="s" s="2">
-        <v>77</v>
+        <v>86</v>
       </c>
       <c r="H18" t="s" s="2">
         <v>78</v>
@@ -3251,22 +3489,24 @@
         <v>78</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>129</v>
+        <v>100</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>130</v>
+        <v>155</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>131</v>
-      </c>
-      <c r="N18" s="2"/>
+        <v>156</v>
+      </c>
+      <c r="N18" t="s" s="2">
+        <v>157</v>
+      </c>
       <c r="O18" s="2"/>
       <c r="P18" t="s" s="2">
         <v>78</v>
       </c>
       <c r="Q18" s="2"/>
       <c r="R18" t="s" s="2">
-        <v>78</v>
+        <v>175</v>
       </c>
       <c r="S18" t="s" s="2">
         <v>78</v>
@@ -3296,29 +3536,31 @@
         <v>78</v>
       </c>
       <c r="AB18" t="s" s="2">
-        <v>132</v>
-      </c>
-      <c r="AC18" s="2"/>
+        <v>78</v>
+      </c>
+      <c r="AC18" t="s" s="2">
+        <v>78</v>
+      </c>
       <c r="AD18" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE18" t="s" s="2">
-        <v>133</v>
+        <v>78</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>188</v>
+        <v>159</v>
       </c>
       <c r="AG18" t="s" s="2">
-        <v>76</v>
+        <v>86</v>
       </c>
       <c r="AH18" t="s" s="2">
-        <v>77</v>
+        <v>86</v>
       </c>
       <c r="AI18" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ18" t="s" s="2">
-        <v>135</v>
+        <v>78</v>
       </c>
       <c r="AK18" t="s" s="2">
         <v>78</v>
@@ -3327,28 +3569,26 @@
         <v>78</v>
       </c>
     </row>
-    <row r="19">
+    <row r="19" hidden="true">
       <c r="A19" t="s" s="2">
-        <v>189</v>
+        <v>176</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>187</v>
-      </c>
-      <c r="C19" t="s" s="2">
-        <v>190</v>
-      </c>
+        <v>161</v>
+      </c>
+      <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
         <v>78</v>
       </c>
       <c r="E19" s="2"/>
       <c r="F19" t="s" s="2">
-        <v>76</v>
+        <v>86</v>
       </c>
       <c r="G19" t="s" s="2">
         <v>86</v>
       </c>
       <c r="H19" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="I19" t="s" s="2">
         <v>78</v>
@@ -3357,17 +3597,15 @@
         <v>78</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>191</v>
+        <v>162</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>192</v>
+        <v>163</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>193</v>
-      </c>
-      <c r="N19" t="s" s="2">
-        <v>194</v>
-      </c>
+        <v>164</v>
+      </c>
+      <c r="N19" s="2"/>
       <c r="O19" s="2"/>
       <c r="P19" t="s" s="2">
         <v>78</v>
@@ -3416,19 +3654,19 @@
         <v>78</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>188</v>
+        <v>165</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH19" t="s" s="2">
-        <v>77</v>
+        <v>86</v>
       </c>
       <c r="AI19" t="s" s="2">
-        <v>141</v>
+        <v>78</v>
       </c>
       <c r="AJ19" t="s" s="2">
-        <v>135</v>
+        <v>98</v>
       </c>
       <c r="AK19" t="s" s="2">
         <v>78</v>
@@ -3439,12 +3677,14 @@
     </row>
     <row r="20" hidden="true">
       <c r="A20" t="s" s="2">
-        <v>195</v>
+        <v>177</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>195</v>
-      </c>
-      <c r="C20" s="2"/>
+        <v>128</v>
+      </c>
+      <c r="C20" t="s" s="2">
+        <v>178</v>
+      </c>
       <c r="D20" t="s" s="2">
         <v>78</v>
       </c>
@@ -3453,7 +3693,7 @@
         <v>76</v>
       </c>
       <c r="G20" t="s" s="2">
-        <v>86</v>
+        <v>77</v>
       </c>
       <c r="H20" t="s" s="2">
         <v>78</v>
@@ -3465,13 +3705,13 @@
         <v>78</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>183</v>
+        <v>179</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>196</v>
+        <v>180</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>196</v>
+        <v>181</v>
       </c>
       <c r="N20" s="2"/>
       <c r="O20" s="2"/>
@@ -3522,19 +3762,19 @@
         <v>78</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>197</v>
+        <v>134</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH20" t="s" s="2">
-        <v>86</v>
+        <v>77</v>
       </c>
       <c r="AI20" t="s" s="2">
-        <v>78</v>
+        <v>142</v>
       </c>
       <c r="AJ20" t="s" s="2">
-        <v>78</v>
+        <v>135</v>
       </c>
       <c r="AK20" t="s" s="2">
         <v>78</v>
@@ -3543,48 +3783,46 @@
         <v>78</v>
       </c>
     </row>
-    <row r="21">
+    <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
-        <v>198</v>
+        <v>182</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>198</v>
-      </c>
-      <c r="C21" s="2"/>
+        <v>128</v>
+      </c>
+      <c r="C21" t="s" s="2">
+        <v>183</v>
+      </c>
       <c r="D21" t="s" s="2">
         <v>78</v>
       </c>
       <c r="E21" s="2"/>
       <c r="F21" t="s" s="2">
-        <v>86</v>
+        <v>76</v>
       </c>
       <c r="G21" t="s" s="2">
         <v>86</v>
       </c>
       <c r="H21" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="I21" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="J21" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>106</v>
+        <v>184</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>199</v>
+        <v>185</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>200</v>
-      </c>
-      <c r="N21" t="s" s="2">
-        <v>201</v>
-      </c>
-      <c r="O21" t="s" s="2">
-        <v>202</v>
-      </c>
+        <v>186</v>
+      </c>
+      <c r="N21" s="2"/>
+      <c r="O21" s="2"/>
       <c r="P21" t="s" s="2">
         <v>78</v>
       </c>
@@ -3608,13 +3846,13 @@
         <v>78</v>
       </c>
       <c r="X21" t="s" s="2">
-        <v>203</v>
+        <v>78</v>
       </c>
       <c r="Y21" t="s" s="2">
-        <v>204</v>
+        <v>78</v>
       </c>
       <c r="Z21" t="s" s="2">
-        <v>205</v>
+        <v>78</v>
       </c>
       <c r="AA21" t="s" s="2">
         <v>78</v>
@@ -3632,68 +3870,68 @@
         <v>78</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>198</v>
+        <v>134</v>
       </c>
       <c r="AG21" t="s" s="2">
-        <v>86</v>
+        <v>76</v>
       </c>
       <c r="AH21" t="s" s="2">
-        <v>86</v>
+        <v>77</v>
       </c>
       <c r="AI21" t="s" s="2">
-        <v>78</v>
+        <v>142</v>
       </c>
       <c r="AJ21" t="s" s="2">
-        <v>98</v>
+        <v>135</v>
       </c>
       <c r="AK21" t="s" s="2">
-        <v>206</v>
+        <v>78</v>
       </c>
       <c r="AL21" t="s" s="2">
-        <v>207</v>
+        <v>78</v>
       </c>
     </row>
-    <row r="22">
+    <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
-        <v>208</v>
+        <v>187</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>208</v>
+        <v>187</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
-        <v>209</v>
+        <v>188</v>
       </c>
       <c r="E22" s="2"/>
       <c r="F22" t="s" s="2">
         <v>76</v>
       </c>
       <c r="G22" t="s" s="2">
-        <v>86</v>
+        <v>77</v>
       </c>
       <c r="H22" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I22" t="s" s="2">
         <v>87</v>
       </c>
-      <c r="I22" t="s" s="2">
-        <v>78</v>
-      </c>
       <c r="J22" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>210</v>
+        <v>129</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>211</v>
+        <v>189</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>212</v>
+        <v>190</v>
       </c>
       <c r="N22" t="s" s="2">
-        <v>213</v>
+        <v>191</v>
       </c>
       <c r="O22" t="s" s="2">
-        <v>214</v>
+        <v>192</v>
       </c>
       <c r="P22" t="s" s="2">
         <v>78</v>
@@ -3742,33 +3980,33 @@
         <v>78</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>208</v>
+        <v>193</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH22" t="s" s="2">
-        <v>86</v>
+        <v>77</v>
       </c>
       <c r="AI22" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ22" t="s" s="2">
-        <v>98</v>
+        <v>135</v>
       </c>
       <c r="AK22" t="s" s="2">
-        <v>215</v>
+        <v>78</v>
       </c>
       <c r="AL22" t="s" s="2">
-        <v>216</v>
+        <v>78</v>
       </c>
     </row>
-    <row r="23" hidden="true">
+    <row r="23">
       <c r="A23" t="s" s="2">
-        <v>217</v>
+        <v>194</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>217</v>
+        <v>194</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -3782,7 +4020,7 @@
         <v>86</v>
       </c>
       <c r="H23" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="I23" t="s" s="2">
         <v>78</v>
@@ -3791,19 +4029,17 @@
         <v>87</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>218</v>
+        <v>195</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>219</v>
+        <v>196</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>220</v>
-      </c>
-      <c r="N23" t="s" s="2">
-        <v>221</v>
-      </c>
+        <v>197</v>
+      </c>
+      <c r="N23" s="2"/>
       <c r="O23" t="s" s="2">
-        <v>222</v>
+        <v>198</v>
       </c>
       <c r="P23" t="s" s="2">
         <v>78</v>
@@ -3852,7 +4088,7 @@
         <v>78</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>217</v>
+        <v>194</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>76</v>
@@ -3867,32 +4103,32 @@
         <v>98</v>
       </c>
       <c r="AK23" t="s" s="2">
-        <v>223</v>
+        <v>199</v>
       </c>
       <c r="AL23" t="s" s="2">
-        <v>224</v>
+        <v>200</v>
       </c>
     </row>
-    <row r="24">
+    <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>225</v>
+        <v>201</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>225</v>
+        <v>201</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
-        <v>226</v>
+        <v>202</v>
       </c>
       <c r="E24" s="2"/>
       <c r="F24" t="s" s="2">
-        <v>86</v>
+        <v>76</v>
       </c>
       <c r="G24" t="s" s="2">
-        <v>86</v>
+        <v>77</v>
       </c>
       <c r="H24" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="I24" t="s" s="2">
         <v>78</v>
@@ -3901,19 +4137,17 @@
         <v>87</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>227</v>
+        <v>203</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>228</v>
+        <v>204</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>229</v>
-      </c>
-      <c r="N24" t="s" s="2">
-        <v>230</v>
-      </c>
+        <v>205</v>
+      </c>
+      <c r="N24" s="2"/>
       <c r="O24" t="s" s="2">
-        <v>231</v>
+        <v>206</v>
       </c>
       <c r="P24" t="s" s="2">
         <v>78</v>
@@ -3962,13 +4196,13 @@
         <v>78</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>225</v>
+        <v>201</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH24" t="s" s="2">
-        <v>86</v>
+        <v>77</v>
       </c>
       <c r="AI24" t="s" s="2">
         <v>78</v>
@@ -3977,32 +4211,32 @@
         <v>98</v>
       </c>
       <c r="AK24" t="s" s="2">
-        <v>232</v>
+        <v>207</v>
       </c>
       <c r="AL24" t="s" s="2">
-        <v>233</v>
+        <v>78</v>
       </c>
     </row>
-    <row r="25">
+    <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>234</v>
+        <v>208</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>234</v>
+        <v>208</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
-        <v>235</v>
+        <v>78</v>
       </c>
       <c r="E25" s="2"/>
       <c r="F25" t="s" s="2">
         <v>76</v>
       </c>
       <c r="G25" t="s" s="2">
-        <v>86</v>
+        <v>77</v>
       </c>
       <c r="H25" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="I25" t="s" s="2">
         <v>78</v>
@@ -4011,20 +4245,18 @@
         <v>87</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>236</v>
+        <v>209</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>237</v>
+        <v>210</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>238</v>
+        <v>211</v>
       </c>
       <c r="N25" t="s" s="2">
-        <v>239</v>
-      </c>
-      <c r="O25" t="s" s="2">
-        <v>240</v>
-      </c>
+        <v>212</v>
+      </c>
+      <c r="O25" s="2"/>
       <c r="P25" t="s" s="2">
         <v>78</v>
       </c>
@@ -4072,13 +4304,13 @@
         <v>78</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>234</v>
+        <v>208</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH25" t="s" s="2">
-        <v>86</v>
+        <v>77</v>
       </c>
       <c r="AI25" t="s" s="2">
         <v>78</v>
@@ -4087,32 +4319,32 @@
         <v>98</v>
       </c>
       <c r="AK25" t="s" s="2">
-        <v>241</v>
+        <v>213</v>
       </c>
       <c r="AL25" t="s" s="2">
-        <v>242</v>
+        <v>78</v>
       </c>
     </row>
-    <row r="26" hidden="true">
+    <row r="26">
       <c r="A26" t="s" s="2">
-        <v>243</v>
+        <v>214</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>243</v>
+        <v>214</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
-        <v>78</v>
+        <v>215</v>
       </c>
       <c r="E26" s="2"/>
       <c r="F26" t="s" s="2">
-        <v>76</v>
+        <v>86</v>
       </c>
       <c r="G26" t="s" s="2">
         <v>86</v>
       </c>
       <c r="H26" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="I26" t="s" s="2">
         <v>78</v>
@@ -4121,19 +4353,19 @@
         <v>87</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>244</v>
+        <v>216</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>245</v>
+        <v>217</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>246</v>
+        <v>218</v>
       </c>
       <c r="N26" t="s" s="2">
-        <v>247</v>
+        <v>219</v>
       </c>
       <c r="O26" t="s" s="2">
-        <v>248</v>
+        <v>220</v>
       </c>
       <c r="P26" t="s" s="2">
         <v>78</v>
@@ -4182,7 +4414,7 @@
         <v>78</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>243</v>
+        <v>214</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>76</v>
@@ -4197,18 +4429,18 @@
         <v>98</v>
       </c>
       <c r="AK26" t="s" s="2">
-        <v>78</v>
+        <v>221</v>
       </c>
       <c r="AL26" t="s" s="2">
-        <v>249</v>
+        <v>78</v>
       </c>
     </row>
-    <row r="27">
+    <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>250</v>
+        <v>222</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>250</v>
+        <v>222</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -4219,10 +4451,10 @@
         <v>76</v>
       </c>
       <c r="G27" t="s" s="2">
-        <v>77</v>
+        <v>86</v>
       </c>
       <c r="H27" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="I27" t="s" s="2">
         <v>78</v>
@@ -4231,17 +4463,15 @@
         <v>78</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>251</v>
+        <v>145</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>252</v>
+        <v>223</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>253</v>
-      </c>
-      <c r="N27" t="s" s="2">
-        <v>254</v>
-      </c>
+        <v>224</v>
+      </c>
+      <c r="N27" s="2"/>
       <c r="O27" s="2"/>
       <c r="P27" t="s" s="2">
         <v>78</v>
@@ -4290,19 +4520,19 @@
         <v>78</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>250</v>
+        <v>148</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH27" t="s" s="2">
-        <v>77</v>
+        <v>86</v>
       </c>
       <c r="AI27" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ27" t="s" s="2">
-        <v>255</v>
+        <v>78</v>
       </c>
       <c r="AK27" t="s" s="2">
         <v>78</v>
@@ -4313,10 +4543,10 @@
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>256</v>
+        <v>225</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>256</v>
+        <v>225</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -4327,7 +4557,7 @@
         <v>76</v>
       </c>
       <c r="G28" t="s" s="2">
-        <v>86</v>
+        <v>77</v>
       </c>
       <c r="H28" t="s" s="2">
         <v>78</v>
@@ -4339,13 +4569,13 @@
         <v>78</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>183</v>
+        <v>129</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>257</v>
+        <v>130</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>258</v>
+        <v>131</v>
       </c>
       <c r="N28" s="2"/>
       <c r="O28" s="2"/>
@@ -4384,31 +4614,29 @@
         <v>78</v>
       </c>
       <c r="AB28" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AC28" t="s" s="2">
-        <v>78</v>
-      </c>
+        <v>132</v>
+      </c>
+      <c r="AC28" s="2"/>
       <c r="AD28" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE28" t="s" s="2">
-        <v>78</v>
+        <v>133</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>186</v>
+        <v>152</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH28" t="s" s="2">
-        <v>86</v>
+        <v>77</v>
       </c>
       <c r="AI28" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ28" t="s" s="2">
-        <v>78</v>
+        <v>135</v>
       </c>
       <c r="AK28" t="s" s="2">
         <v>78</v>
@@ -4417,14 +4645,16 @@
         <v>78</v>
       </c>
     </row>
-    <row r="29" hidden="true">
+    <row r="29">
       <c r="A29" t="s" s="2">
-        <v>259</v>
+        <v>226</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>259</v>
-      </c>
-      <c r="C29" s="2"/>
+        <v>225</v>
+      </c>
+      <c r="C29" t="s" s="2">
+        <v>227</v>
+      </c>
       <c r="D29" t="s" s="2">
         <v>78</v>
       </c>
@@ -4433,10 +4663,10 @@
         <v>76</v>
       </c>
       <c r="G29" t="s" s="2">
-        <v>77</v>
+        <v>86</v>
       </c>
       <c r="H29" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="I29" t="s" s="2">
         <v>78</v>
@@ -4445,15 +4675,17 @@
         <v>78</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>129</v>
+        <v>228</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>130</v>
+        <v>229</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>131</v>
-      </c>
-      <c r="N29" s="2"/>
+        <v>230</v>
+      </c>
+      <c r="N29" t="s" s="2">
+        <v>231</v>
+      </c>
       <c r="O29" s="2"/>
       <c r="P29" t="s" s="2">
         <v>78</v>
@@ -4490,17 +4722,19 @@
         <v>78</v>
       </c>
       <c r="AB29" t="s" s="2">
-        <v>132</v>
-      </c>
-      <c r="AC29" s="2"/>
+        <v>78</v>
+      </c>
+      <c r="AC29" t="s" s="2">
+        <v>78</v>
+      </c>
       <c r="AD29" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE29" t="s" s="2">
-        <v>133</v>
+        <v>78</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>188</v>
+        <v>152</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>76</v>
@@ -4509,7 +4743,7 @@
         <v>77</v>
       </c>
       <c r="AI29" t="s" s="2">
-        <v>78</v>
+        <v>142</v>
       </c>
       <c r="AJ29" t="s" s="2">
         <v>135</v>
@@ -4523,14 +4757,12 @@
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>260</v>
+        <v>232</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>259</v>
-      </c>
-      <c r="C30" t="s" s="2">
-        <v>261</v>
-      </c>
+        <v>232</v>
+      </c>
+      <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
         <v>78</v>
       </c>
@@ -4551,13 +4783,13 @@
         <v>78</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>262</v>
+        <v>145</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>263</v>
+        <v>233</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>264</v>
+        <v>233</v>
       </c>
       <c r="N30" s="2"/>
       <c r="O30" s="2"/>
@@ -4608,19 +4840,19 @@
         <v>78</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>188</v>
+        <v>234</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH30" t="s" s="2">
-        <v>77</v>
+        <v>86</v>
       </c>
       <c r="AI30" t="s" s="2">
-        <v>141</v>
+        <v>78</v>
       </c>
       <c r="AJ30" t="s" s="2">
-        <v>135</v>
+        <v>78</v>
       </c>
       <c r="AK30" t="s" s="2">
         <v>78</v>
@@ -4629,46 +4861,48 @@
         <v>78</v>
       </c>
     </row>
-    <row r="31" hidden="true">
+    <row r="31">
       <c r="A31" t="s" s="2">
-        <v>265</v>
+        <v>235</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>259</v>
-      </c>
-      <c r="C31" t="s" s="2">
-        <v>266</v>
-      </c>
+        <v>235</v>
+      </c>
+      <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
         <v>78</v>
       </c>
       <c r="E31" s="2"/>
       <c r="F31" t="s" s="2">
-        <v>76</v>
+        <v>86</v>
       </c>
       <c r="G31" t="s" s="2">
-        <v>77</v>
+        <v>86</v>
       </c>
       <c r="H31" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="I31" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="J31" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>138</v>
+        <v>106</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>139</v>
+        <v>236</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>140</v>
-      </c>
-      <c r="N31" s="2"/>
-      <c r="O31" s="2"/>
+        <v>237</v>
+      </c>
+      <c r="N31" t="s" s="2">
+        <v>238</v>
+      </c>
+      <c r="O31" t="s" s="2">
+        <v>239</v>
+      </c>
       <c r="P31" t="s" s="2">
         <v>78</v>
       </c>
@@ -4692,13 +4926,13 @@
         <v>78</v>
       </c>
       <c r="X31" t="s" s="2">
-        <v>78</v>
+        <v>240</v>
       </c>
       <c r="Y31" t="s" s="2">
-        <v>78</v>
+        <v>241</v>
       </c>
       <c r="Z31" t="s" s="2">
-        <v>78</v>
+        <v>242</v>
       </c>
       <c r="AA31" t="s" s="2">
         <v>78</v>
@@ -4716,68 +4950,68 @@
         <v>78</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>188</v>
+        <v>235</v>
       </c>
       <c r="AG31" t="s" s="2">
-        <v>76</v>
+        <v>86</v>
       </c>
       <c r="AH31" t="s" s="2">
-        <v>77</v>
+        <v>86</v>
       </c>
       <c r="AI31" t="s" s="2">
-        <v>141</v>
+        <v>78</v>
       </c>
       <c r="AJ31" t="s" s="2">
-        <v>135</v>
+        <v>98</v>
       </c>
       <c r="AK31" t="s" s="2">
-        <v>78</v>
+        <v>243</v>
       </c>
       <c r="AL31" t="s" s="2">
-        <v>78</v>
+        <v>244</v>
       </c>
     </row>
-    <row r="32" hidden="true">
+    <row r="32">
       <c r="A32" t="s" s="2">
-        <v>267</v>
+        <v>245</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>267</v>
+        <v>245</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
-        <v>268</v>
+        <v>246</v>
       </c>
       <c r="E32" s="2"/>
       <c r="F32" t="s" s="2">
         <v>76</v>
       </c>
       <c r="G32" t="s" s="2">
-        <v>77</v>
+        <v>86</v>
       </c>
       <c r="H32" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="I32" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="J32" t="s" s="2">
         <v>87</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>129</v>
+        <v>247</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>269</v>
+        <v>248</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>270</v>
+        <v>249</v>
       </c>
       <c r="N32" t="s" s="2">
-        <v>151</v>
+        <v>250</v>
       </c>
       <c r="O32" t="s" s="2">
-        <v>152</v>
+        <v>251</v>
       </c>
       <c r="P32" t="s" s="2">
         <v>78</v>
@@ -4826,33 +5060,33 @@
         <v>78</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>271</v>
+        <v>245</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH32" t="s" s="2">
-        <v>77</v>
+        <v>86</v>
       </c>
       <c r="AI32" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ32" t="s" s="2">
-        <v>135</v>
+        <v>98</v>
       </c>
       <c r="AK32" t="s" s="2">
-        <v>78</v>
+        <v>252</v>
       </c>
       <c r="AL32" t="s" s="2">
-        <v>78</v>
+        <v>253</v>
       </c>
     </row>
-    <row r="33">
+    <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>272</v>
+        <v>254</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>272</v>
+        <v>254</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -4860,32 +5094,34 @@
       </c>
       <c r="E33" s="2"/>
       <c r="F33" t="s" s="2">
-        <v>86</v>
+        <v>76</v>
       </c>
       <c r="G33" t="s" s="2">
         <v>86</v>
       </c>
       <c r="H33" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I33" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J33" t="s" s="2">
         <v>87</v>
       </c>
-      <c r="I33" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="J33" t="s" s="2">
-        <v>78</v>
-      </c>
       <c r="K33" t="s" s="2">
-        <v>183</v>
+        <v>255</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>273</v>
+        <v>256</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>274</v>
-      </c>
-      <c r="N33" s="2"/>
+        <v>257</v>
+      </c>
+      <c r="N33" t="s" s="2">
+        <v>258</v>
+      </c>
       <c r="O33" t="s" s="2">
-        <v>275</v>
+        <v>259</v>
       </c>
       <c r="P33" t="s" s="2">
         <v>78</v>
@@ -4934,10 +5170,10 @@
         <v>78</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>272</v>
+        <v>254</v>
       </c>
       <c r="AG33" t="s" s="2">
-        <v>86</v>
+        <v>76</v>
       </c>
       <c r="AH33" t="s" s="2">
         <v>86</v>
@@ -4949,53 +5185,53 @@
         <v>98</v>
       </c>
       <c r="AK33" t="s" s="2">
-        <v>78</v>
+        <v>260</v>
       </c>
       <c r="AL33" t="s" s="2">
-        <v>78</v>
+        <v>261</v>
       </c>
     </row>
-    <row r="34" hidden="true">
+    <row r="34">
       <c r="A34" t="s" s="2">
-        <v>276</v>
+        <v>262</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>276</v>
+        <v>262</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
-        <v>78</v>
+        <v>263</v>
       </c>
       <c r="E34" s="2"/>
       <c r="F34" t="s" s="2">
-        <v>76</v>
+        <v>86</v>
       </c>
       <c r="G34" t="s" s="2">
         <v>86</v>
       </c>
       <c r="H34" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="I34" t="s" s="2">
         <v>78</v>
       </c>
       <c r="J34" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>100</v>
+        <v>264</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>277</v>
+        <v>265</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>278</v>
+        <v>266</v>
       </c>
       <c r="N34" t="s" s="2">
-        <v>279</v>
+        <v>267</v>
       </c>
       <c r="O34" t="s" s="2">
-        <v>280</v>
+        <v>268</v>
       </c>
       <c r="P34" t="s" s="2">
         <v>78</v>
@@ -5044,7 +5280,7 @@
         <v>78</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>276</v>
+        <v>262</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>76</v>
@@ -5059,22 +5295,22 @@
         <v>98</v>
       </c>
       <c r="AK34" t="s" s="2">
-        <v>78</v>
+        <v>269</v>
       </c>
       <c r="AL34" t="s" s="2">
-        <v>78</v>
+        <v>270</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
-        <v>281</v>
+        <v>271</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>281</v>
+        <v>271</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
-        <v>78</v>
+        <v>272</v>
       </c>
       <c r="E35" s="2"/>
       <c r="F35" t="s" s="2">
@@ -5090,20 +5326,22 @@
         <v>78</v>
       </c>
       <c r="J35" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>183</v>
+        <v>273</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>282</v>
+        <v>274</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>283</v>
-      </c>
-      <c r="N35" s="2"/>
+        <v>275</v>
+      </c>
+      <c r="N35" t="s" s="2">
+        <v>276</v>
+      </c>
       <c r="O35" t="s" s="2">
-        <v>284</v>
+        <v>277</v>
       </c>
       <c r="P35" t="s" s="2">
         <v>78</v>
@@ -5152,7 +5390,7 @@
         <v>78</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>281</v>
+        <v>271</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>76</v>
@@ -5167,18 +5405,18 @@
         <v>98</v>
       </c>
       <c r="AK35" t="s" s="2">
-        <v>78</v>
+        <v>278</v>
       </c>
       <c r="AL35" t="s" s="2">
-        <v>78</v>
+        <v>279</v>
       </c>
     </row>
-    <row r="36">
+    <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>285</v>
+        <v>280</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>285</v>
+        <v>280</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -5189,30 +5427,32 @@
         <v>76</v>
       </c>
       <c r="G36" t="s" s="2">
-        <v>77</v>
+        <v>86</v>
       </c>
       <c r="H36" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I36" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J36" t="s" s="2">
         <v>87</v>
       </c>
-      <c r="I36" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="J36" t="s" s="2">
-        <v>78</v>
-      </c>
       <c r="K36" t="s" s="2">
-        <v>251</v>
+        <v>281</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>286</v>
+        <v>282</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>287</v>
+        <v>283</v>
       </c>
       <c r="N36" t="s" s="2">
-        <v>288</v>
-      </c>
-      <c r="O36" s="2"/>
+        <v>284</v>
+      </c>
+      <c r="O36" t="s" s="2">
+        <v>285</v>
+      </c>
       <c r="P36" t="s" s="2">
         <v>78</v>
       </c>
@@ -5260,13 +5500,13 @@
         <v>78</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>285</v>
+        <v>280</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH36" t="s" s="2">
-        <v>77</v>
+        <v>86</v>
       </c>
       <c r="AI36" t="s" s="2">
         <v>78</v>
@@ -5278,15 +5518,15 @@
         <v>78</v>
       </c>
       <c r="AL36" t="s" s="2">
-        <v>78</v>
+        <v>286</v>
       </c>
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -5309,13 +5549,13 @@
         <v>78</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>183</v>
+        <v>145</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>257</v>
+        <v>146</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>258</v>
+        <v>147</v>
       </c>
       <c r="N37" s="2"/>
       <c r="O37" s="2"/>
@@ -5366,7 +5606,7 @@
         <v>78</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>186</v>
+        <v>148</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>76</v>
@@ -5389,14 +5629,14 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
-        <v>78</v>
+        <v>188</v>
       </c>
       <c r="E38" s="2"/>
       <c r="F38" t="s" s="2">
@@ -5418,12 +5658,14 @@
         <v>129</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>130</v>
+        <v>289</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>131</v>
-      </c>
-      <c r="N38" s="2"/>
+        <v>290</v>
+      </c>
+      <c r="N38" t="s" s="2">
+        <v>191</v>
+      </c>
       <c r="O38" s="2"/>
       <c r="P38" t="s" s="2">
         <v>78</v>
@@ -5462,7 +5704,9 @@
       <c r="AB38" t="s" s="2">
         <v>132</v>
       </c>
-      <c r="AC38" s="2"/>
+      <c r="AC38" t="s" s="2">
+        <v>151</v>
+      </c>
       <c r="AD38" t="s" s="2">
         <v>78</v>
       </c>
@@ -5470,7 +5714,7 @@
         <v>133</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>188</v>
+        <v>152</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>76</v>
@@ -5496,7 +5740,7 @@
         <v>291</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="C39" t="s" s="2">
         <v>292</v>
@@ -5529,7 +5773,9 @@
       <c r="M39" t="s" s="2">
         <v>295</v>
       </c>
-      <c r="N39" s="2"/>
+      <c r="N39" t="s" s="2">
+        <v>296</v>
+      </c>
       <c r="O39" s="2"/>
       <c r="P39" t="s" s="2">
         <v>78</v>
@@ -5578,7 +5824,7 @@
         <v>78</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>188</v>
+        <v>152</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>76</v>
@@ -5587,7 +5833,7 @@
         <v>77</v>
       </c>
       <c r="AI39" t="s" s="2">
-        <v>141</v>
+        <v>78</v>
       </c>
       <c r="AJ39" t="s" s="2">
         <v>135</v>
@@ -5601,14 +5847,12 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>290</v>
-      </c>
-      <c r="C40" t="s" s="2">
-        <v>297</v>
-      </c>
+        <v>298</v>
+      </c>
+      <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
         <v>78</v>
       </c>
@@ -5629,17 +5873,15 @@
         <v>78</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>298</v>
+        <v>145</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>299</v>
+        <v>146</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>300</v>
-      </c>
-      <c r="N40" t="s" s="2">
-        <v>301</v>
-      </c>
+        <v>147</v>
+      </c>
+      <c r="N40" s="2"/>
       <c r="O40" s="2"/>
       <c r="P40" t="s" s="2">
         <v>78</v>
@@ -5688,19 +5930,19 @@
         <v>78</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>188</v>
+        <v>148</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH40" t="s" s="2">
-        <v>77</v>
+        <v>86</v>
       </c>
       <c r="AI40" t="s" s="2">
-        <v>141</v>
+        <v>78</v>
       </c>
       <c r="AJ40" t="s" s="2">
-        <v>135</v>
+        <v>78</v>
       </c>
       <c r="AK40" t="s" s="2">
         <v>78</v>
@@ -5711,46 +5953,42 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>302</v>
+        <v>299</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
-        <v>268</v>
+        <v>78</v>
       </c>
       <c r="E41" s="2"/>
       <c r="F41" t="s" s="2">
         <v>76</v>
       </c>
       <c r="G41" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="H41" t="s" s="2">
         <v>78</v>
       </c>
       <c r="I41" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="J41" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="K41" t="s" s="2">
         <v>129</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>269</v>
+        <v>130</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>270</v>
-      </c>
-      <c r="N41" t="s" s="2">
-        <v>151</v>
-      </c>
-      <c r="O41" t="s" s="2">
-        <v>152</v>
-      </c>
+        <v>131</v>
+      </c>
+      <c r="N41" s="2"/>
+      <c r="O41" s="2"/>
       <c r="P41" t="s" s="2">
         <v>78</v>
       </c>
@@ -5786,19 +6024,19 @@
         <v>78</v>
       </c>
       <c r="AB41" t="s" s="2">
-        <v>78</v>
+        <v>132</v>
       </c>
       <c r="AC41" t="s" s="2">
-        <v>78</v>
+        <v>151</v>
       </c>
       <c r="AD41" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE41" t="s" s="2">
-        <v>78</v>
+        <v>133</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>271</v>
+        <v>152</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>76</v>
@@ -5819,12 +6057,12 @@
         <v>78</v>
       </c>
     </row>
-    <row r="42">
+    <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -5832,13 +6070,13 @@
       </c>
       <c r="E42" s="2"/>
       <c r="F42" t="s" s="2">
-        <v>76</v>
+        <v>86</v>
       </c>
       <c r="G42" t="s" s="2">
         <v>86</v>
       </c>
       <c r="H42" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="I42" t="s" s="2">
         <v>78</v>
@@ -5847,26 +6085,24 @@
         <v>78</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>304</v>
+        <v>100</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>305</v>
+        <v>155</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>306</v>
+        <v>156</v>
       </c>
       <c r="N42" t="s" s="2">
-        <v>307</v>
-      </c>
-      <c r="O42" t="s" s="2">
-        <v>308</v>
-      </c>
+        <v>157</v>
+      </c>
+      <c r="O42" s="2"/>
       <c r="P42" t="s" s="2">
         <v>78</v>
       </c>
       <c r="Q42" s="2"/>
       <c r="R42" t="s" s="2">
-        <v>78</v>
+        <v>303</v>
       </c>
       <c r="S42" t="s" s="2">
         <v>78</v>
@@ -5884,13 +6120,13 @@
         <v>78</v>
       </c>
       <c r="X42" t="s" s="2">
-        <v>309</v>
+        <v>78</v>
       </c>
       <c r="Y42" t="s" s="2">
-        <v>310</v>
+        <v>78</v>
       </c>
       <c r="Z42" t="s" s="2">
-        <v>311</v>
+        <v>78</v>
       </c>
       <c r="AA42" t="s" s="2">
         <v>78</v>
@@ -5908,10 +6144,10 @@
         <v>78</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>303</v>
+        <v>159</v>
       </c>
       <c r="AG42" t="s" s="2">
-        <v>76</v>
+        <v>86</v>
       </c>
       <c r="AH42" t="s" s="2">
         <v>86</v>
@@ -5920,7 +6156,7 @@
         <v>78</v>
       </c>
       <c r="AJ42" t="s" s="2">
-        <v>98</v>
+        <v>78</v>
       </c>
       <c r="AK42" t="s" s="2">
         <v>78</v>
@@ -5929,12 +6165,12 @@
         <v>78</v>
       </c>
     </row>
-    <row r="43">
+    <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>312</v>
+        <v>304</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>312</v>
+        <v>305</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -5942,13 +6178,13 @@
       </c>
       <c r="E43" s="2"/>
       <c r="F43" t="s" s="2">
-        <v>76</v>
+        <v>86</v>
       </c>
       <c r="G43" t="s" s="2">
-        <v>77</v>
+        <v>86</v>
       </c>
       <c r="H43" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="I43" t="s" s="2">
         <v>78</v>
@@ -5957,18 +6193,16 @@
         <v>78</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>79</v>
+        <v>306</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>313</v>
+        <v>163</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>314</v>
+        <v>164</v>
       </c>
       <c r="N43" s="2"/>
-      <c r="O43" t="s" s="2">
-        <v>315</v>
-      </c>
+      <c r="O43" s="2"/>
       <c r="P43" t="s" s="2">
         <v>78</v>
       </c>
@@ -6016,13 +6250,13 @@
         <v>78</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>312</v>
+        <v>165</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH43" t="s" s="2">
-        <v>77</v>
+        <v>86</v>
       </c>
       <c r="AI43" t="s" s="2">
         <v>78</v>
@@ -6037,12 +6271,12 @@
         <v>78</v>
       </c>
     </row>
-    <row r="44">
+    <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>316</v>
+        <v>307</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>316</v>
+        <v>307</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -6053,30 +6287,30 @@
         <v>76</v>
       </c>
       <c r="G44" t="s" s="2">
-        <v>77</v>
+        <v>86</v>
       </c>
       <c r="H44" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I44" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J44" t="s" s="2">
         <v>87</v>
       </c>
-      <c r="I44" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="J44" t="s" s="2">
-        <v>78</v>
-      </c>
       <c r="K44" t="s" s="2">
-        <v>79</v>
+        <v>145</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>317</v>
+        <v>308</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>318</v>
-      </c>
-      <c r="N44" s="2"/>
-      <c r="O44" t="s" s="2">
-        <v>319</v>
-      </c>
+        <v>309</v>
+      </c>
+      <c r="N44" t="s" s="2">
+        <v>310</v>
+      </c>
+      <c r="O44" s="2"/>
       <c r="P44" t="s" s="2">
         <v>78</v>
       </c>
@@ -6124,16 +6358,16 @@
         <v>78</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>316</v>
+        <v>311</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH44" t="s" s="2">
-        <v>77</v>
+        <v>86</v>
       </c>
       <c r="AI44" t="s" s="2">
-        <v>78</v>
+        <v>312</v>
       </c>
       <c r="AJ44" t="s" s="2">
         <v>98</v>
@@ -6145,8 +6379,2274 @@
         <v>78</v>
       </c>
     </row>
+    <row r="45" hidden="true">
+      <c r="A45" t="s" s="2">
+        <v>313</v>
+      </c>
+      <c r="B45" t="s" s="2">
+        <v>313</v>
+      </c>
+      <c r="C45" s="2"/>
+      <c r="D45" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="E45" s="2"/>
+      <c r="F45" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="G45" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="H45" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I45" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J45" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="K45" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="L45" t="s" s="2">
+        <v>314</v>
+      </c>
+      <c r="M45" t="s" s="2">
+        <v>315</v>
+      </c>
+      <c r="N45" t="s" s="2">
+        <v>316</v>
+      </c>
+      <c r="O45" s="2"/>
+      <c r="P45" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Q45" s="2"/>
+      <c r="R45" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="S45" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T45" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U45" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V45" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W45" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X45" t="s" s="2">
+        <v>317</v>
+      </c>
+      <c r="Y45" t="s" s="2">
+        <v>318</v>
+      </c>
+      <c r="Z45" t="s" s="2">
+        <v>319</v>
+      </c>
+      <c r="AA45" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB45" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC45" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD45" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE45" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF45" t="s" s="2">
+        <v>320</v>
+      </c>
+      <c r="AG45" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AH45" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="AI45" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AJ45" t="s" s="2">
+        <v>98</v>
+      </c>
+      <c r="AK45" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL45" t="s" s="2">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="46" hidden="true">
+      <c r="A46" t="s" s="2">
+        <v>321</v>
+      </c>
+      <c r="B46" t="s" s="2">
+        <v>321</v>
+      </c>
+      <c r="C46" s="2"/>
+      <c r="D46" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="E46" s="2"/>
+      <c r="F46" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="G46" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="H46" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I46" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J46" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="K46" t="s" s="2">
+        <v>195</v>
+      </c>
+      <c r="L46" t="s" s="2">
+        <v>322</v>
+      </c>
+      <c r="M46" t="s" s="2">
+        <v>323</v>
+      </c>
+      <c r="N46" t="s" s="2">
+        <v>324</v>
+      </c>
+      <c r="O46" s="2"/>
+      <c r="P46" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Q46" s="2"/>
+      <c r="R46" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="S46" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T46" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U46" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V46" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W46" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X46" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y46" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z46" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA46" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB46" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC46" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD46" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE46" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF46" t="s" s="2">
+        <v>325</v>
+      </c>
+      <c r="AG46" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AH46" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="AI46" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AJ46" t="s" s="2">
+        <v>98</v>
+      </c>
+      <c r="AK46" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL46" t="s" s="2">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="47" hidden="true">
+      <c r="A47" t="s" s="2">
+        <v>326</v>
+      </c>
+      <c r="B47" t="s" s="2">
+        <v>326</v>
+      </c>
+      <c r="C47" s="2"/>
+      <c r="D47" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="E47" s="2"/>
+      <c r="F47" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="G47" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="H47" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I47" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J47" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="K47" t="s" s="2">
+        <v>145</v>
+      </c>
+      <c r="L47" t="s" s="2">
+        <v>327</v>
+      </c>
+      <c r="M47" t="s" s="2">
+        <v>328</v>
+      </c>
+      <c r="N47" t="s" s="2">
+        <v>329</v>
+      </c>
+      <c r="O47" s="2"/>
+      <c r="P47" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Q47" s="2"/>
+      <c r="R47" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="S47" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T47" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U47" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V47" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W47" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X47" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y47" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z47" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA47" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB47" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC47" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD47" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE47" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF47" t="s" s="2">
+        <v>330</v>
+      </c>
+      <c r="AG47" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AH47" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="AI47" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AJ47" t="s" s="2">
+        <v>98</v>
+      </c>
+      <c r="AK47" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL47" t="s" s="2">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="s" s="2">
+        <v>331</v>
+      </c>
+      <c r="B48" t="s" s="2">
+        <v>331</v>
+      </c>
+      <c r="C48" s="2"/>
+      <c r="D48" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="E48" s="2"/>
+      <c r="F48" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="G48" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="H48" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="I48" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J48" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="K48" t="s" s="2">
+        <v>332</v>
+      </c>
+      <c r="L48" t="s" s="2">
+        <v>333</v>
+      </c>
+      <c r="M48" t="s" s="2">
+        <v>334</v>
+      </c>
+      <c r="N48" t="s" s="2">
+        <v>335</v>
+      </c>
+      <c r="O48" s="2"/>
+      <c r="P48" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Q48" s="2"/>
+      <c r="R48" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="S48" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T48" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U48" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V48" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W48" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X48" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y48" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z48" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA48" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB48" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC48" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD48" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE48" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF48" t="s" s="2">
+        <v>331</v>
+      </c>
+      <c r="AG48" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AH48" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AI48" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AJ48" t="s" s="2">
+        <v>336</v>
+      </c>
+      <c r="AK48" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL48" t="s" s="2">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="49" hidden="true">
+      <c r="A49" t="s" s="2">
+        <v>337</v>
+      </c>
+      <c r="B49" t="s" s="2">
+        <v>337</v>
+      </c>
+      <c r="C49" s="2"/>
+      <c r="D49" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="E49" s="2"/>
+      <c r="F49" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="G49" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="H49" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I49" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J49" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="K49" t="s" s="2">
+        <v>145</v>
+      </c>
+      <c r="L49" t="s" s="2">
+        <v>146</v>
+      </c>
+      <c r="M49" t="s" s="2">
+        <v>147</v>
+      </c>
+      <c r="N49" s="2"/>
+      <c r="O49" s="2"/>
+      <c r="P49" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Q49" s="2"/>
+      <c r="R49" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="S49" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T49" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U49" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V49" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W49" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X49" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y49" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z49" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA49" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB49" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC49" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD49" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE49" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF49" t="s" s="2">
+        <v>148</v>
+      </c>
+      <c r="AG49" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AH49" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="AI49" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AJ49" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AK49" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL49" t="s" s="2">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="50" hidden="true">
+      <c r="A50" t="s" s="2">
+        <v>338</v>
+      </c>
+      <c r="B50" t="s" s="2">
+        <v>338</v>
+      </c>
+      <c r="C50" s="2"/>
+      <c r="D50" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="E50" s="2"/>
+      <c r="F50" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="G50" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="H50" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I50" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J50" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="K50" t="s" s="2">
+        <v>129</v>
+      </c>
+      <c r="L50" t="s" s="2">
+        <v>130</v>
+      </c>
+      <c r="M50" t="s" s="2">
+        <v>131</v>
+      </c>
+      <c r="N50" s="2"/>
+      <c r="O50" s="2"/>
+      <c r="P50" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Q50" s="2"/>
+      <c r="R50" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="S50" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T50" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U50" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V50" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W50" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X50" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y50" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z50" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA50" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB50" t="s" s="2">
+        <v>132</v>
+      </c>
+      <c r="AC50" s="2"/>
+      <c r="AD50" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE50" t="s" s="2">
+        <v>133</v>
+      </c>
+      <c r="AF50" t="s" s="2">
+        <v>152</v>
+      </c>
+      <c r="AG50" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AH50" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AI50" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AJ50" t="s" s="2">
+        <v>135</v>
+      </c>
+      <c r="AK50" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL50" t="s" s="2">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="51" hidden="true">
+      <c r="A51" t="s" s="2">
+        <v>339</v>
+      </c>
+      <c r="B51" t="s" s="2">
+        <v>338</v>
+      </c>
+      <c r="C51" t="s" s="2">
+        <v>340</v>
+      </c>
+      <c r="D51" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="E51" s="2"/>
+      <c r="F51" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="G51" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="H51" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I51" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J51" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="K51" t="s" s="2">
+        <v>341</v>
+      </c>
+      <c r="L51" t="s" s="2">
+        <v>342</v>
+      </c>
+      <c r="M51" t="s" s="2">
+        <v>343</v>
+      </c>
+      <c r="N51" s="2"/>
+      <c r="O51" s="2"/>
+      <c r="P51" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Q51" s="2"/>
+      <c r="R51" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="S51" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T51" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U51" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V51" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W51" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X51" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y51" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z51" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA51" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB51" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC51" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD51" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE51" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF51" t="s" s="2">
+        <v>152</v>
+      </c>
+      <c r="AG51" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AH51" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AI51" t="s" s="2">
+        <v>142</v>
+      </c>
+      <c r="AJ51" t="s" s="2">
+        <v>135</v>
+      </c>
+      <c r="AK51" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL51" t="s" s="2">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="52" hidden="true">
+      <c r="A52" t="s" s="2">
+        <v>344</v>
+      </c>
+      <c r="B52" t="s" s="2">
+        <v>338</v>
+      </c>
+      <c r="C52" t="s" s="2">
+        <v>345</v>
+      </c>
+      <c r="D52" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="E52" s="2"/>
+      <c r="F52" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="G52" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="H52" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I52" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J52" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="K52" t="s" s="2">
+        <v>179</v>
+      </c>
+      <c r="L52" t="s" s="2">
+        <v>180</v>
+      </c>
+      <c r="M52" t="s" s="2">
+        <v>181</v>
+      </c>
+      <c r="N52" s="2"/>
+      <c r="O52" s="2"/>
+      <c r="P52" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Q52" s="2"/>
+      <c r="R52" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="S52" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T52" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U52" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V52" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W52" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X52" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y52" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z52" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA52" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB52" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC52" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD52" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE52" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF52" t="s" s="2">
+        <v>152</v>
+      </c>
+      <c r="AG52" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AH52" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AI52" t="s" s="2">
+        <v>142</v>
+      </c>
+      <c r="AJ52" t="s" s="2">
+        <v>135</v>
+      </c>
+      <c r="AK52" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL52" t="s" s="2">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="53" hidden="true">
+      <c r="A53" t="s" s="2">
+        <v>346</v>
+      </c>
+      <c r="B53" t="s" s="2">
+        <v>346</v>
+      </c>
+      <c r="C53" s="2"/>
+      <c r="D53" t="s" s="2">
+        <v>347</v>
+      </c>
+      <c r="E53" s="2"/>
+      <c r="F53" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="G53" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="H53" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I53" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="J53" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="K53" t="s" s="2">
+        <v>129</v>
+      </c>
+      <c r="L53" t="s" s="2">
+        <v>348</v>
+      </c>
+      <c r="M53" t="s" s="2">
+        <v>349</v>
+      </c>
+      <c r="N53" t="s" s="2">
+        <v>191</v>
+      </c>
+      <c r="O53" t="s" s="2">
+        <v>192</v>
+      </c>
+      <c r="P53" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Q53" s="2"/>
+      <c r="R53" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="S53" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T53" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U53" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V53" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W53" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X53" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y53" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z53" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA53" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB53" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC53" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD53" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE53" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF53" t="s" s="2">
+        <v>350</v>
+      </c>
+      <c r="AG53" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AH53" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AI53" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AJ53" t="s" s="2">
+        <v>135</v>
+      </c>
+      <c r="AK53" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL53" t="s" s="2">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="s" s="2">
+        <v>351</v>
+      </c>
+      <c r="B54" t="s" s="2">
+        <v>351</v>
+      </c>
+      <c r="C54" s="2"/>
+      <c r="D54" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="E54" s="2"/>
+      <c r="F54" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="G54" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="H54" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="I54" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J54" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="K54" t="s" s="2">
+        <v>145</v>
+      </c>
+      <c r="L54" t="s" s="2">
+        <v>352</v>
+      </c>
+      <c r="M54" t="s" s="2">
+        <v>353</v>
+      </c>
+      <c r="N54" s="2"/>
+      <c r="O54" t="s" s="2">
+        <v>354</v>
+      </c>
+      <c r="P54" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Q54" s="2"/>
+      <c r="R54" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="S54" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T54" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U54" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V54" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W54" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X54" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y54" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z54" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA54" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB54" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC54" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD54" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE54" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF54" t="s" s="2">
+        <v>351</v>
+      </c>
+      <c r="AG54" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="AH54" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="AI54" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AJ54" t="s" s="2">
+        <v>98</v>
+      </c>
+      <c r="AK54" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL54" t="s" s="2">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="55" hidden="true">
+      <c r="A55" t="s" s="2">
+        <v>355</v>
+      </c>
+      <c r="B55" t="s" s="2">
+        <v>355</v>
+      </c>
+      <c r="C55" s="2"/>
+      <c r="D55" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="E55" s="2"/>
+      <c r="F55" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="G55" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="H55" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I55" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J55" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="K55" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="L55" t="s" s="2">
+        <v>356</v>
+      </c>
+      <c r="M55" t="s" s="2">
+        <v>357</v>
+      </c>
+      <c r="N55" t="s" s="2">
+        <v>358</v>
+      </c>
+      <c r="O55" t="s" s="2">
+        <v>359</v>
+      </c>
+      <c r="P55" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Q55" s="2"/>
+      <c r="R55" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="S55" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T55" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U55" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V55" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W55" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X55" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y55" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z55" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA55" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB55" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC55" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD55" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE55" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF55" t="s" s="2">
+        <v>355</v>
+      </c>
+      <c r="AG55" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AH55" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="AI55" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AJ55" t="s" s="2">
+        <v>98</v>
+      </c>
+      <c r="AK55" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL55" t="s" s="2">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="s" s="2">
+        <v>360</v>
+      </c>
+      <c r="B56" t="s" s="2">
+        <v>360</v>
+      </c>
+      <c r="C56" s="2"/>
+      <c r="D56" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="E56" s="2"/>
+      <c r="F56" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="G56" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="H56" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="I56" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J56" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="K56" t="s" s="2">
+        <v>145</v>
+      </c>
+      <c r="L56" t="s" s="2">
+        <v>361</v>
+      </c>
+      <c r="M56" t="s" s="2">
+        <v>362</v>
+      </c>
+      <c r="N56" s="2"/>
+      <c r="O56" t="s" s="2">
+        <v>363</v>
+      </c>
+      <c r="P56" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Q56" s="2"/>
+      <c r="R56" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="S56" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T56" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U56" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V56" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W56" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X56" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y56" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z56" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA56" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB56" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC56" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD56" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE56" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF56" t="s" s="2">
+        <v>360</v>
+      </c>
+      <c r="AG56" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AH56" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="AI56" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AJ56" t="s" s="2">
+        <v>98</v>
+      </c>
+      <c r="AK56" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL56" t="s" s="2">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="s" s="2">
+        <v>364</v>
+      </c>
+      <c r="B57" t="s" s="2">
+        <v>364</v>
+      </c>
+      <c r="C57" s="2"/>
+      <c r="D57" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="E57" s="2"/>
+      <c r="F57" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="G57" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="H57" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="I57" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J57" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="K57" t="s" s="2">
+        <v>332</v>
+      </c>
+      <c r="L57" t="s" s="2">
+        <v>365</v>
+      </c>
+      <c r="M57" t="s" s="2">
+        <v>366</v>
+      </c>
+      <c r="N57" t="s" s="2">
+        <v>367</v>
+      </c>
+      <c r="O57" s="2"/>
+      <c r="P57" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Q57" s="2"/>
+      <c r="R57" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="S57" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T57" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U57" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V57" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W57" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X57" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y57" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z57" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA57" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB57" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC57" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD57" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE57" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF57" t="s" s="2">
+        <v>364</v>
+      </c>
+      <c r="AG57" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AH57" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AI57" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AJ57" t="s" s="2">
+        <v>98</v>
+      </c>
+      <c r="AK57" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL57" t="s" s="2">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="58" hidden="true">
+      <c r="A58" t="s" s="2">
+        <v>368</v>
+      </c>
+      <c r="B58" t="s" s="2">
+        <v>368</v>
+      </c>
+      <c r="C58" s="2"/>
+      <c r="D58" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="E58" s="2"/>
+      <c r="F58" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="G58" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="H58" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I58" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J58" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="K58" t="s" s="2">
+        <v>145</v>
+      </c>
+      <c r="L58" t="s" s="2">
+        <v>146</v>
+      </c>
+      <c r="M58" t="s" s="2">
+        <v>147</v>
+      </c>
+      <c r="N58" s="2"/>
+      <c r="O58" s="2"/>
+      <c r="P58" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Q58" s="2"/>
+      <c r="R58" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="S58" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T58" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U58" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V58" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W58" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X58" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y58" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z58" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA58" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB58" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC58" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD58" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE58" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF58" t="s" s="2">
+        <v>148</v>
+      </c>
+      <c r="AG58" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AH58" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="AI58" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AJ58" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AK58" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL58" t="s" s="2">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="59" hidden="true">
+      <c r="A59" t="s" s="2">
+        <v>369</v>
+      </c>
+      <c r="B59" t="s" s="2">
+        <v>369</v>
+      </c>
+      <c r="C59" s="2"/>
+      <c r="D59" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="E59" s="2"/>
+      <c r="F59" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="G59" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="H59" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I59" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J59" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="K59" t="s" s="2">
+        <v>129</v>
+      </c>
+      <c r="L59" t="s" s="2">
+        <v>130</v>
+      </c>
+      <c r="M59" t="s" s="2">
+        <v>131</v>
+      </c>
+      <c r="N59" s="2"/>
+      <c r="O59" s="2"/>
+      <c r="P59" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Q59" s="2"/>
+      <c r="R59" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="S59" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T59" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U59" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V59" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W59" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X59" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y59" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z59" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA59" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB59" t="s" s="2">
+        <v>132</v>
+      </c>
+      <c r="AC59" s="2"/>
+      <c r="AD59" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE59" t="s" s="2">
+        <v>133</v>
+      </c>
+      <c r="AF59" t="s" s="2">
+        <v>152</v>
+      </c>
+      <c r="AG59" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AH59" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AI59" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AJ59" t="s" s="2">
+        <v>135</v>
+      </c>
+      <c r="AK59" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL59" t="s" s="2">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="60" hidden="true">
+      <c r="A60" t="s" s="2">
+        <v>370</v>
+      </c>
+      <c r="B60" t="s" s="2">
+        <v>369</v>
+      </c>
+      <c r="C60" t="s" s="2">
+        <v>371</v>
+      </c>
+      <c r="D60" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="E60" s="2"/>
+      <c r="F60" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="G60" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="H60" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I60" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J60" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="K60" t="s" s="2">
+        <v>372</v>
+      </c>
+      <c r="L60" t="s" s="2">
+        <v>373</v>
+      </c>
+      <c r="M60" t="s" s="2">
+        <v>374</v>
+      </c>
+      <c r="N60" s="2"/>
+      <c r="O60" s="2"/>
+      <c r="P60" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Q60" s="2"/>
+      <c r="R60" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="S60" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T60" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U60" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V60" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W60" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X60" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y60" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z60" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA60" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB60" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC60" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD60" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE60" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF60" t="s" s="2">
+        <v>152</v>
+      </c>
+      <c r="AG60" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AH60" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AI60" t="s" s="2">
+        <v>142</v>
+      </c>
+      <c r="AJ60" t="s" s="2">
+        <v>135</v>
+      </c>
+      <c r="AK60" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL60" t="s" s="2">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="61" hidden="true">
+      <c r="A61" t="s" s="2">
+        <v>375</v>
+      </c>
+      <c r="B61" t="s" s="2">
+        <v>369</v>
+      </c>
+      <c r="C61" t="s" s="2">
+        <v>376</v>
+      </c>
+      <c r="D61" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="E61" s="2"/>
+      <c r="F61" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="G61" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="H61" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I61" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J61" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="K61" t="s" s="2">
+        <v>377</v>
+      </c>
+      <c r="L61" t="s" s="2">
+        <v>378</v>
+      </c>
+      <c r="M61" t="s" s="2">
+        <v>379</v>
+      </c>
+      <c r="N61" t="s" s="2">
+        <v>380</v>
+      </c>
+      <c r="O61" s="2"/>
+      <c r="P61" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Q61" s="2"/>
+      <c r="R61" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="S61" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T61" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U61" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V61" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W61" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X61" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y61" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z61" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA61" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB61" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC61" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD61" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE61" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF61" t="s" s="2">
+        <v>152</v>
+      </c>
+      <c r="AG61" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AH61" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AI61" t="s" s="2">
+        <v>142</v>
+      </c>
+      <c r="AJ61" t="s" s="2">
+        <v>135</v>
+      </c>
+      <c r="AK61" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL61" t="s" s="2">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="62" hidden="true">
+      <c r="A62" t="s" s="2">
+        <v>381</v>
+      </c>
+      <c r="B62" t="s" s="2">
+        <v>381</v>
+      </c>
+      <c r="C62" s="2"/>
+      <c r="D62" t="s" s="2">
+        <v>347</v>
+      </c>
+      <c r="E62" s="2"/>
+      <c r="F62" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="G62" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="H62" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I62" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="J62" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="K62" t="s" s="2">
+        <v>129</v>
+      </c>
+      <c r="L62" t="s" s="2">
+        <v>348</v>
+      </c>
+      <c r="M62" t="s" s="2">
+        <v>349</v>
+      </c>
+      <c r="N62" t="s" s="2">
+        <v>191</v>
+      </c>
+      <c r="O62" t="s" s="2">
+        <v>192</v>
+      </c>
+      <c r="P62" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Q62" s="2"/>
+      <c r="R62" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="S62" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T62" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U62" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V62" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W62" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X62" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y62" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z62" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA62" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB62" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC62" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD62" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE62" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF62" t="s" s="2">
+        <v>350</v>
+      </c>
+      <c r="AG62" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AH62" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AI62" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AJ62" t="s" s="2">
+        <v>135</v>
+      </c>
+      <c r="AK62" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL62" t="s" s="2">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="s" s="2">
+        <v>382</v>
+      </c>
+      <c r="B63" t="s" s="2">
+        <v>382</v>
+      </c>
+      <c r="C63" s="2"/>
+      <c r="D63" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="E63" s="2"/>
+      <c r="F63" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="G63" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="H63" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="I63" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J63" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="K63" t="s" s="2">
+        <v>383</v>
+      </c>
+      <c r="L63" t="s" s="2">
+        <v>384</v>
+      </c>
+      <c r="M63" t="s" s="2">
+        <v>385</v>
+      </c>
+      <c r="N63" t="s" s="2">
+        <v>386</v>
+      </c>
+      <c r="O63" t="s" s="2">
+        <v>387</v>
+      </c>
+      <c r="P63" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Q63" s="2"/>
+      <c r="R63" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="S63" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T63" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U63" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V63" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W63" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X63" t="s" s="2">
+        <v>388</v>
+      </c>
+      <c r="Y63" t="s" s="2">
+        <v>389</v>
+      </c>
+      <c r="Z63" t="s" s="2">
+        <v>390</v>
+      </c>
+      <c r="AA63" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB63" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC63" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD63" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE63" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF63" t="s" s="2">
+        <v>382</v>
+      </c>
+      <c r="AG63" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AH63" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="AI63" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AJ63" t="s" s="2">
+        <v>98</v>
+      </c>
+      <c r="AK63" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL63" t="s" s="2">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="s" s="2">
+        <v>391</v>
+      </c>
+      <c r="B64" t="s" s="2">
+        <v>391</v>
+      </c>
+      <c r="C64" s="2"/>
+      <c r="D64" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="E64" s="2"/>
+      <c r="F64" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="G64" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="H64" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="I64" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J64" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="K64" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="L64" t="s" s="2">
+        <v>392</v>
+      </c>
+      <c r="M64" t="s" s="2">
+        <v>393</v>
+      </c>
+      <c r="N64" s="2"/>
+      <c r="O64" t="s" s="2">
+        <v>394</v>
+      </c>
+      <c r="P64" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Q64" s="2"/>
+      <c r="R64" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="S64" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T64" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U64" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V64" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W64" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X64" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y64" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z64" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA64" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB64" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC64" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD64" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE64" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF64" t="s" s="2">
+        <v>391</v>
+      </c>
+      <c r="AG64" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AH64" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AI64" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AJ64" t="s" s="2">
+        <v>98</v>
+      </c>
+      <c r="AK64" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL64" t="s" s="2">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="s" s="2">
+        <v>395</v>
+      </c>
+      <c r="B65" t="s" s="2">
+        <v>395</v>
+      </c>
+      <c r="C65" s="2"/>
+      <c r="D65" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="E65" s="2"/>
+      <c r="F65" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="G65" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="H65" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="I65" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J65" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="K65" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="L65" t="s" s="2">
+        <v>396</v>
+      </c>
+      <c r="M65" t="s" s="2">
+        <v>397</v>
+      </c>
+      <c r="N65" s="2"/>
+      <c r="O65" t="s" s="2">
+        <v>398</v>
+      </c>
+      <c r="P65" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Q65" s="2"/>
+      <c r="R65" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="S65" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T65" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U65" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V65" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W65" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X65" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y65" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z65" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA65" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB65" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC65" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD65" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE65" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF65" t="s" s="2">
+        <v>395</v>
+      </c>
+      <c r="AG65" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AH65" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AI65" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AJ65" t="s" s="2">
+        <v>98</v>
+      </c>
+      <c r="AK65" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL65" t="s" s="2">
+        <v>78</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:AL44">
+  <autoFilter ref="A1:AL65">
     <filterColumn colId="7">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -6156,7 +8656,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI43">
+  <conditionalFormatting sqref="A2:AI64">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>

--- a/StructureDefinition-mii-pr-pro-questionnaire-response.xlsx
+++ b/StructureDefinition-mii-pr-pro-questionnaire-response.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AL$65</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AL$81</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2245" uniqueCount="399">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2783" uniqueCount="459">
   <si>
     <t>Property</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2027.0.0-ballot.rc4</t>
+    <t>2027.0.0-ballot.rc5</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-08T17:30:22+00:00</t>
+    <t>2026-09-11T10:35:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -347,7 +347,7 @@
 </t>
   </si>
   <si>
-    <t>Language of the resource content</t>
+    <t>Sprache der Antwortinhalte</t>
   </si>
   <si>
     <t>The base language in which the resource is written.</t>
@@ -1156,13 +1156,50 @@
     <t>QuestionnaireResponse.item.text</t>
   </si>
   <si>
-    <t>Name for group or question text</t>
+    <t>Wortlaut des Items, wie er der antwortenden Person präsentiert wurde</t>
   </si>
   <si>
     <t>Text that is displayed above the contents of the group or as the text of the question being answered.</t>
   </si>
   <si>
     <t>Allows the questionnaire response to be read without access to the questionnaire.</t>
+  </si>
+  <si>
+    <t>QuestionnaireResponse.item.text.id</t>
+  </si>
+  <si>
+    <t>QuestionnaireResponse.item.text.extension</t>
+  </si>
+  <si>
+    <t>QuestionnaireResponse.item.text.extension:translation</t>
+  </si>
+  <si>
+    <t>translation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extension {translation}
+</t>
+  </si>
+  <si>
+    <t>Language Translation (Localization)</t>
+  </si>
+  <si>
+    <t>Language translation from base language of resource to another language, used to provide translations for strings, including markdown. Generally, the type of the translation extension SHOULD match that of the element being extended.</t>
+  </si>
+  <si>
+    <t>QuestionnaireResponse.item.text.value</t>
+  </si>
+  <si>
+    <t>Primitive value for string</t>
+  </si>
+  <si>
+    <t>The actual value</t>
+  </si>
+  <si>
+    <t>1048576</t>
+  </si>
+  <si>
+    <t>string.value</t>
   </si>
   <si>
     <t>QuestionnaireResponse.item.answer</t>
@@ -1247,6 +1284,153 @@
   </si>
   <si>
     <t>http://hl7.org/fhir/ValueSet/questionnaire-answers|4.0.1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">type:$this}
+</t>
+  </si>
+  <si>
+    <t>QuestionnaireResponse.item.answer.value[x]:valueCoding</t>
+  </si>
+  <si>
+    <t>valueCoding</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Coding
+</t>
+  </si>
+  <si>
+    <t>QuestionnaireResponse.item.answer.value[x]:valueCoding.id</t>
+  </si>
+  <si>
+    <t>QuestionnaireResponse.item.answer.value[x].id</t>
+  </si>
+  <si>
+    <t>QuestionnaireResponse.item.answer.value[x]:valueCoding.extension</t>
+  </si>
+  <si>
+    <t>QuestionnaireResponse.item.answer.value[x].extension</t>
+  </si>
+  <si>
+    <t>QuestionnaireResponse.item.answer.value[x]:valueCoding.system</t>
+  </si>
+  <si>
+    <t>QuestionnaireResponse.item.answer.value[x].system</t>
+  </si>
+  <si>
+    <t>Identity of the terminology system</t>
+  </si>
+  <si>
+    <t>The identification of the code system that defines the meaning of the symbol in the code.</t>
+  </si>
+  <si>
+    <t>The URI may be an OID (urn:oid:...) or a UUID (urn:uuid:...).  OIDs and UUIDs SHALL be references to the HL7 OID registry. Otherwise, the URI should come from HL7's list of FHIR defined special URIs or it should reference to some definition that establishes the system clearly and unambiguously.</t>
+  </si>
+  <si>
+    <t>Need to be unambiguous about the source of the definition of the symbol.</t>
+  </si>
+  <si>
+    <t>Coding.system</t>
+  </si>
+  <si>
+    <t>QuestionnaireResponse.item.answer.value[x]:valueCoding.version</t>
+  </si>
+  <si>
+    <t>QuestionnaireResponse.item.answer.value[x].version</t>
+  </si>
+  <si>
+    <t>Version of the system - if relevant</t>
+  </si>
+  <si>
+    <t>The version of the code system which was used when choosing this code. Note that a well-maintained code system does not need the version reported, because the meaning of codes is consistent across versions. However this cannot consistently be assured, and when the meaning is not guaranteed to be consistent, the version SHOULD be exchanged.</t>
+  </si>
+  <si>
+    <t>Where the terminology does not clearly define what string should be used to identify code system versions, the recommendation is to use the date (expressed in FHIR date format) on which that version was officially published as the version date.</t>
+  </si>
+  <si>
+    <t>Coding.version</t>
+  </si>
+  <si>
+    <t>QuestionnaireResponse.item.answer.value[x]:valueCoding.code</t>
+  </si>
+  <si>
+    <t>QuestionnaireResponse.item.answer.value[x].code</t>
+  </si>
+  <si>
+    <t>Symbol in syntax defined by the system</t>
+  </si>
+  <si>
+    <t>A symbol in syntax defined by the system. The symbol may be a predefined code or an expression in a syntax defined by the coding system (e.g. post-coordination).</t>
+  </si>
+  <si>
+    <t>Need to refer to a particular code in the system.</t>
+  </si>
+  <si>
+    <t>Coding.code</t>
+  </si>
+  <si>
+    <t>QuestionnaireResponse.item.answer.value[x]:valueCoding.display</t>
+  </si>
+  <si>
+    <t>QuestionnaireResponse.item.answer.value[x].display</t>
+  </si>
+  <si>
+    <t>Wortlaut der gewählten Antwort</t>
+  </si>
+  <si>
+    <t>A representation of the meaning of the code in the system, following the rules of the system.</t>
+  </si>
+  <si>
+    <t>Need to be able to carry a human-readable meaning of the code for readers that do not know  the system.</t>
+  </si>
+  <si>
+    <t>Coding.display</t>
+  </si>
+  <si>
+    <t>QuestionnaireResponse.item.answer.value[x]:valueCoding.display.id</t>
+  </si>
+  <si>
+    <t>QuestionnaireResponse.item.answer.value[x].display.id</t>
+  </si>
+  <si>
+    <t>QuestionnaireResponse.item.answer.value[x]:valueCoding.display.extension</t>
+  </si>
+  <si>
+    <t>QuestionnaireResponse.item.answer.value[x].display.extension</t>
+  </si>
+  <si>
+    <t>QuestionnaireResponse.item.answer.value[x]:valueCoding.display.extension:translation</t>
+  </si>
+  <si>
+    <t>QuestionnaireResponse.item.answer.value[x]:valueCoding.display.value</t>
+  </si>
+  <si>
+    <t>QuestionnaireResponse.item.answer.value[x].display.value</t>
+  </si>
+  <si>
+    <t>QuestionnaireResponse.item.answer.value[x]:valueCoding.userSelected</t>
+  </si>
+  <si>
+    <t>QuestionnaireResponse.item.answer.value[x].userSelected</t>
+  </si>
+  <si>
+    <t xml:space="preserve">boolean
+</t>
+  </si>
+  <si>
+    <t>If this coding was chosen directly by the user</t>
+  </si>
+  <si>
+    <t>Indicates that this coding was chosen by a user directly - e.g. off a pick list of available items (codes or displays).</t>
+  </si>
+  <si>
+    <t>Amongst a set of alternatives, a directly chosen code is the most appropriate starting point for new translations. There is some ambiguity about what exactly 'directly chosen' implies, and trading partner agreement may be needed to clarify the use of this element and its consequences more completely.</t>
+  </si>
+  <si>
+    <t>This has been identified as a clinical safety criterium - that this exact system/code pair was chosen explicitly, rather than inferred by the system based on some rules or language processing.</t>
+  </si>
+  <si>
+    <t>Coding.userSelected</t>
   </si>
   <si>
     <t>QuestionnaireResponse.item.answer.item</t>
@@ -1587,11 +1771,11 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AL65"/>
+  <dimension ref="A1:AL81"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="56.1640625" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="44.52734375" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="70.29296875" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="51.0" customWidth="true" bestFit="true"/>
     <col min="3" max="3" width="17.48828125" customWidth="true" bestFit="true" hidden="true"/>
     <col min="4" max="4" width="40.65625" customWidth="true" bestFit="true" hidden="true"/>
     <col min="5" max="5" width="5.80859375" customWidth="true" bestFit="true"/>
@@ -7673,7 +7857,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="57">
+    <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
         <v>364</v>
       </c>
@@ -7689,10 +7873,10 @@
         <v>76</v>
       </c>
       <c r="G57" t="s" s="2">
-        <v>77</v>
+        <v>86</v>
       </c>
       <c r="H57" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="I57" t="s" s="2">
         <v>78</v>
@@ -7701,17 +7885,15 @@
         <v>78</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>332</v>
+        <v>145</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>365</v>
+        <v>223</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>366</v>
-      </c>
-      <c r="N57" t="s" s="2">
-        <v>367</v>
-      </c>
+        <v>224</v>
+      </c>
+      <c r="N57" s="2"/>
       <c r="O57" s="2"/>
       <c r="P57" t="s" s="2">
         <v>78</v>
@@ -7760,19 +7942,19 @@
         <v>78</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>364</v>
+        <v>148</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH57" t="s" s="2">
-        <v>77</v>
+        <v>86</v>
       </c>
       <c r="AI57" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ57" t="s" s="2">
-        <v>98</v>
+        <v>78</v>
       </c>
       <c r="AK57" t="s" s="2">
         <v>78</v>
@@ -7783,10 +7965,10 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>368</v>
+        <v>365</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>368</v>
+        <v>365</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -7797,7 +7979,7 @@
         <v>76</v>
       </c>
       <c r="G58" t="s" s="2">
-        <v>86</v>
+        <v>77</v>
       </c>
       <c r="H58" t="s" s="2">
         <v>78</v>
@@ -7809,13 +7991,13 @@
         <v>78</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>145</v>
+        <v>129</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>146</v>
+        <v>130</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>147</v>
+        <v>131</v>
       </c>
       <c r="N58" s="2"/>
       <c r="O58" s="2"/>
@@ -7854,31 +8036,29 @@
         <v>78</v>
       </c>
       <c r="AB58" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AC58" t="s" s="2">
-        <v>78</v>
-      </c>
+        <v>132</v>
+      </c>
+      <c r="AC58" s="2"/>
       <c r="AD58" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE58" t="s" s="2">
-        <v>78</v>
+        <v>133</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH58" t="s" s="2">
-        <v>86</v>
+        <v>77</v>
       </c>
       <c r="AI58" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ58" t="s" s="2">
-        <v>78</v>
+        <v>135</v>
       </c>
       <c r="AK58" t="s" s="2">
         <v>78</v>
@@ -7887,14 +8067,16 @@
         <v>78</v>
       </c>
     </row>
-    <row r="59" hidden="true">
+    <row r="59">
       <c r="A59" t="s" s="2">
-        <v>369</v>
+        <v>366</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>369</v>
-      </c>
-      <c r="C59" s="2"/>
+        <v>365</v>
+      </c>
+      <c r="C59" t="s" s="2">
+        <v>367</v>
+      </c>
       <c r="D59" t="s" s="2">
         <v>78</v>
       </c>
@@ -7906,7 +8088,7 @@
         <v>77</v>
       </c>
       <c r="H59" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="I59" t="s" s="2">
         <v>78</v>
@@ -7915,13 +8097,13 @@
         <v>78</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>129</v>
+        <v>368</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>130</v>
+        <v>369</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>131</v>
+        <v>370</v>
       </c>
       <c r="N59" s="2"/>
       <c r="O59" s="2"/>
@@ -7960,14 +8142,16 @@
         <v>78</v>
       </c>
       <c r="AB59" t="s" s="2">
-        <v>132</v>
-      </c>
-      <c r="AC59" s="2"/>
+        <v>78</v>
+      </c>
+      <c r="AC59" t="s" s="2">
+        <v>78</v>
+      </c>
       <c r="AD59" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE59" t="s" s="2">
-        <v>133</v>
+        <v>78</v>
       </c>
       <c r="AF59" t="s" s="2">
         <v>152</v>
@@ -7979,7 +8163,7 @@
         <v>77</v>
       </c>
       <c r="AI59" t="s" s="2">
-        <v>78</v>
+        <v>142</v>
       </c>
       <c r="AJ59" t="s" s="2">
         <v>135</v>
@@ -7993,14 +8177,12 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>369</v>
-      </c>
-      <c r="C60" t="s" s="2">
         <v>371</v>
       </c>
+      <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
         <v>78</v>
       </c>
@@ -8021,13 +8203,13 @@
         <v>78</v>
       </c>
       <c r="K60" t="s" s="2">
+        <v>145</v>
+      </c>
+      <c r="L60" t="s" s="2">
         <v>372</v>
       </c>
-      <c r="L60" t="s" s="2">
+      <c r="M60" t="s" s="2">
         <v>373</v>
-      </c>
-      <c r="M60" t="s" s="2">
-        <v>374</v>
       </c>
       <c r="N60" s="2"/>
       <c r="O60" s="2"/>
@@ -8051,7 +8233,7 @@
         <v>78</v>
       </c>
       <c r="W60" t="s" s="2">
-        <v>78</v>
+        <v>374</v>
       </c>
       <c r="X60" t="s" s="2">
         <v>78</v>
@@ -8078,19 +8260,19 @@
         <v>78</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>152</v>
+        <v>375</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH60" t="s" s="2">
-        <v>77</v>
+        <v>86</v>
       </c>
       <c r="AI60" t="s" s="2">
-        <v>142</v>
+        <v>78</v>
       </c>
       <c r="AJ60" t="s" s="2">
-        <v>135</v>
+        <v>78</v>
       </c>
       <c r="AK60" t="s" s="2">
         <v>78</v>
@@ -8099,16 +8281,14 @@
         <v>78</v>
       </c>
     </row>
-    <row r="61" hidden="true">
+    <row r="61">
       <c r="A61" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>369</v>
-      </c>
-      <c r="C61" t="s" s="2">
         <v>376</v>
       </c>
+      <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
         <v>78</v>
       </c>
@@ -8117,10 +8297,10 @@
         <v>76</v>
       </c>
       <c r="G61" t="s" s="2">
-        <v>86</v>
+        <v>77</v>
       </c>
       <c r="H61" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="I61" t="s" s="2">
         <v>78</v>
@@ -8129,16 +8309,16 @@
         <v>78</v>
       </c>
       <c r="K61" t="s" s="2">
+        <v>332</v>
+      </c>
+      <c r="L61" t="s" s="2">
         <v>377</v>
       </c>
-      <c r="L61" t="s" s="2">
+      <c r="M61" t="s" s="2">
         <v>378</v>
       </c>
-      <c r="M61" t="s" s="2">
+      <c r="N61" t="s" s="2">
         <v>379</v>
-      </c>
-      <c r="N61" t="s" s="2">
-        <v>380</v>
       </c>
       <c r="O61" s="2"/>
       <c r="P61" t="s" s="2">
@@ -8188,7 +8368,7 @@
         <v>78</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>152</v>
+        <v>376</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>76</v>
@@ -8197,10 +8377,10 @@
         <v>77</v>
       </c>
       <c r="AI61" t="s" s="2">
-        <v>142</v>
+        <v>78</v>
       </c>
       <c r="AJ61" t="s" s="2">
-        <v>135</v>
+        <v>98</v>
       </c>
       <c r="AK61" t="s" s="2">
         <v>78</v>
@@ -8211,46 +8391,42 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
-        <v>347</v>
+        <v>78</v>
       </c>
       <c r="E62" s="2"/>
       <c r="F62" t="s" s="2">
         <v>76</v>
       </c>
       <c r="G62" t="s" s="2">
-        <v>77</v>
+        <v>86</v>
       </c>
       <c r="H62" t="s" s="2">
         <v>78</v>
       </c>
       <c r="I62" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="J62" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>129</v>
+        <v>145</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>348</v>
+        <v>146</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>349</v>
-      </c>
-      <c r="N62" t="s" s="2">
-        <v>191</v>
-      </c>
-      <c r="O62" t="s" s="2">
-        <v>192</v>
-      </c>
+        <v>147</v>
+      </c>
+      <c r="N62" s="2"/>
+      <c r="O62" s="2"/>
       <c r="P62" t="s" s="2">
         <v>78</v>
       </c>
@@ -8298,19 +8474,19 @@
         <v>78</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>350</v>
+        <v>148</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH62" t="s" s="2">
-        <v>77</v>
+        <v>86</v>
       </c>
       <c r="AI62" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ62" t="s" s="2">
-        <v>135</v>
+        <v>78</v>
       </c>
       <c r="AK62" t="s" s="2">
         <v>78</v>
@@ -8319,12 +8495,12 @@
         <v>78</v>
       </c>
     </row>
-    <row r="63">
+    <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -8335,10 +8511,10 @@
         <v>76</v>
       </c>
       <c r="G63" t="s" s="2">
-        <v>86</v>
+        <v>77</v>
       </c>
       <c r="H63" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="I63" t="s" s="2">
         <v>78</v>
@@ -8347,20 +8523,16 @@
         <v>78</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>383</v>
+        <v>129</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>384</v>
+        <v>130</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>385</v>
-      </c>
-      <c r="N63" t="s" s="2">
-        <v>386</v>
-      </c>
-      <c r="O63" t="s" s="2">
-        <v>387</v>
-      </c>
+        <v>131</v>
+      </c>
+      <c r="N63" s="2"/>
+      <c r="O63" s="2"/>
       <c r="P63" t="s" s="2">
         <v>78</v>
       </c>
@@ -8384,59 +8556,59 @@
         <v>78</v>
       </c>
       <c r="X63" t="s" s="2">
-        <v>388</v>
+        <v>78</v>
       </c>
       <c r="Y63" t="s" s="2">
-        <v>389</v>
+        <v>78</v>
       </c>
       <c r="Z63" t="s" s="2">
-        <v>390</v>
+        <v>78</v>
       </c>
       <c r="AA63" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AB63" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AC63" t="s" s="2">
-        <v>78</v>
-      </c>
+        <v>132</v>
+      </c>
+      <c r="AC63" s="2"/>
       <c r="AD63" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE63" t="s" s="2">
-        <v>78</v>
+        <v>133</v>
       </c>
       <c r="AF63" t="s" s="2">
+        <v>152</v>
+      </c>
+      <c r="AG63" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AH63" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AI63" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AJ63" t="s" s="2">
+        <v>135</v>
+      </c>
+      <c r="AK63" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL63" t="s" s="2">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="64" hidden="true">
+      <c r="A64" t="s" s="2">
         <v>382</v>
       </c>
-      <c r="AG63" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AH63" t="s" s="2">
-        <v>86</v>
-      </c>
-      <c r="AI63" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AJ63" t="s" s="2">
-        <v>98</v>
-      </c>
-      <c r="AK63" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AL63" t="s" s="2">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" t="s" s="2">
-        <v>391</v>
-      </c>
       <c r="B64" t="s" s="2">
-        <v>391</v>
-      </c>
-      <c r="C64" s="2"/>
+        <v>381</v>
+      </c>
+      <c r="C64" t="s" s="2">
+        <v>383</v>
+      </c>
       <c r="D64" t="s" s="2">
         <v>78</v>
       </c>
@@ -8445,10 +8617,10 @@
         <v>76</v>
       </c>
       <c r="G64" t="s" s="2">
-        <v>77</v>
+        <v>86</v>
       </c>
       <c r="H64" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="I64" t="s" s="2">
         <v>78</v>
@@ -8457,18 +8629,16 @@
         <v>78</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>79</v>
+        <v>384</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>392</v>
+        <v>385</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>393</v>
+        <v>386</v>
       </c>
       <c r="N64" s="2"/>
-      <c r="O64" t="s" s="2">
-        <v>394</v>
-      </c>
+      <c r="O64" s="2"/>
       <c r="P64" t="s" s="2">
         <v>78</v>
       </c>
@@ -8516,7 +8686,7 @@
         <v>78</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>391</v>
+        <v>152</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>76</v>
@@ -8525,10 +8695,10 @@
         <v>77</v>
       </c>
       <c r="AI64" t="s" s="2">
-        <v>78</v>
+        <v>142</v>
       </c>
       <c r="AJ64" t="s" s="2">
-        <v>98</v>
+        <v>135</v>
       </c>
       <c r="AK64" t="s" s="2">
         <v>78</v>
@@ -8537,14 +8707,16 @@
         <v>78</v>
       </c>
     </row>
-    <row r="65">
+    <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>395</v>
+        <v>387</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>395</v>
-      </c>
-      <c r="C65" s="2"/>
+        <v>381</v>
+      </c>
+      <c r="C65" t="s" s="2">
+        <v>388</v>
+      </c>
       <c r="D65" t="s" s="2">
         <v>78</v>
       </c>
@@ -8553,10 +8725,10 @@
         <v>76</v>
       </c>
       <c r="G65" t="s" s="2">
-        <v>77</v>
+        <v>86</v>
       </c>
       <c r="H65" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="I65" t="s" s="2">
         <v>78</v>
@@ -8565,18 +8737,18 @@
         <v>78</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>79</v>
+        <v>389</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>396</v>
+        <v>390</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>397</v>
-      </c>
-      <c r="N65" s="2"/>
-      <c r="O65" t="s" s="2">
-        <v>398</v>
-      </c>
+        <v>391</v>
+      </c>
+      <c r="N65" t="s" s="2">
+        <v>392</v>
+      </c>
+      <c r="O65" s="2"/>
       <c r="P65" t="s" s="2">
         <v>78</v>
       </c>
@@ -8624,7 +8796,7 @@
         <v>78</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>395</v>
+        <v>152</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>76</v>
@@ -8633,20 +8805,1748 @@
         <v>77</v>
       </c>
       <c r="AI65" t="s" s="2">
-        <v>78</v>
+        <v>142</v>
       </c>
       <c r="AJ65" t="s" s="2">
+        <v>135</v>
+      </c>
+      <c r="AK65" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL65" t="s" s="2">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="66" hidden="true">
+      <c r="A66" t="s" s="2">
+        <v>393</v>
+      </c>
+      <c r="B66" t="s" s="2">
+        <v>393</v>
+      </c>
+      <c r="C66" s="2"/>
+      <c r="D66" t="s" s="2">
+        <v>347</v>
+      </c>
+      <c r="E66" s="2"/>
+      <c r="F66" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="G66" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="H66" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I66" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="J66" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="K66" t="s" s="2">
+        <v>129</v>
+      </c>
+      <c r="L66" t="s" s="2">
+        <v>348</v>
+      </c>
+      <c r="M66" t="s" s="2">
+        <v>349</v>
+      </c>
+      <c r="N66" t="s" s="2">
+        <v>191</v>
+      </c>
+      <c r="O66" t="s" s="2">
+        <v>192</v>
+      </c>
+      <c r="P66" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Q66" s="2"/>
+      <c r="R66" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="S66" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T66" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U66" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V66" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W66" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X66" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y66" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z66" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA66" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB66" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC66" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD66" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE66" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF66" t="s" s="2">
+        <v>350</v>
+      </c>
+      <c r="AG66" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AH66" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AI66" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AJ66" t="s" s="2">
+        <v>135</v>
+      </c>
+      <c r="AK66" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL66" t="s" s="2">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="67" hidden="true">
+      <c r="A67" t="s" s="2">
+        <v>394</v>
+      </c>
+      <c r="B67" t="s" s="2">
+        <v>394</v>
+      </c>
+      <c r="C67" s="2"/>
+      <c r="D67" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="E67" s="2"/>
+      <c r="F67" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="G67" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="H67" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="I67" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J67" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="K67" t="s" s="2">
+        <v>395</v>
+      </c>
+      <c r="L67" t="s" s="2">
+        <v>396</v>
+      </c>
+      <c r="M67" t="s" s="2">
+        <v>397</v>
+      </c>
+      <c r="N67" t="s" s="2">
+        <v>398</v>
+      </c>
+      <c r="O67" t="s" s="2">
+        <v>399</v>
+      </c>
+      <c r="P67" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Q67" s="2"/>
+      <c r="R67" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="S67" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T67" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U67" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V67" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W67" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X67" t="s" s="2">
+        <v>400</v>
+      </c>
+      <c r="Y67" t="s" s="2">
+        <v>401</v>
+      </c>
+      <c r="Z67" t="s" s="2">
+        <v>402</v>
+      </c>
+      <c r="AA67" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB67" t="s" s="2">
+        <v>403</v>
+      </c>
+      <c r="AC67" s="2"/>
+      <c r="AD67" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE67" t="s" s="2">
+        <v>133</v>
+      </c>
+      <c r="AF67" t="s" s="2">
+        <v>394</v>
+      </c>
+      <c r="AG67" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AH67" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="AI67" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AJ67" t="s" s="2">
         <v>98</v>
       </c>
-      <c r="AK65" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AL65" t="s" s="2">
+      <c r="AK67" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL67" t="s" s="2">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="s" s="2">
+        <v>404</v>
+      </c>
+      <c r="B68" t="s" s="2">
+        <v>394</v>
+      </c>
+      <c r="C68" t="s" s="2">
+        <v>405</v>
+      </c>
+      <c r="D68" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="E68" s="2"/>
+      <c r="F68" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="G68" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="H68" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="I68" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J68" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="K68" t="s" s="2">
+        <v>406</v>
+      </c>
+      <c r="L68" t="s" s="2">
+        <v>396</v>
+      </c>
+      <c r="M68" t="s" s="2">
+        <v>397</v>
+      </c>
+      <c r="N68" t="s" s="2">
+        <v>398</v>
+      </c>
+      <c r="O68" t="s" s="2">
+        <v>399</v>
+      </c>
+      <c r="P68" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Q68" s="2"/>
+      <c r="R68" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="S68" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T68" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U68" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V68" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W68" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X68" t="s" s="2">
+        <v>400</v>
+      </c>
+      <c r="Y68" t="s" s="2">
+        <v>401</v>
+      </c>
+      <c r="Z68" t="s" s="2">
+        <v>402</v>
+      </c>
+      <c r="AA68" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB68" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC68" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD68" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE68" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF68" t="s" s="2">
+        <v>394</v>
+      </c>
+      <c r="AG68" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AH68" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="AI68" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AJ68" t="s" s="2">
+        <v>98</v>
+      </c>
+      <c r="AK68" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL68" t="s" s="2">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="69" hidden="true">
+      <c r="A69" t="s" s="2">
+        <v>407</v>
+      </c>
+      <c r="B69" t="s" s="2">
+        <v>408</v>
+      </c>
+      <c r="C69" s="2"/>
+      <c r="D69" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="E69" s="2"/>
+      <c r="F69" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="G69" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="H69" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I69" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J69" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="K69" t="s" s="2">
+        <v>145</v>
+      </c>
+      <c r="L69" t="s" s="2">
+        <v>146</v>
+      </c>
+      <c r="M69" t="s" s="2">
+        <v>147</v>
+      </c>
+      <c r="N69" s="2"/>
+      <c r="O69" s="2"/>
+      <c r="P69" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Q69" s="2"/>
+      <c r="R69" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="S69" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T69" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U69" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V69" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W69" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X69" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y69" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z69" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA69" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB69" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC69" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD69" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE69" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF69" t="s" s="2">
+        <v>148</v>
+      </c>
+      <c r="AG69" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AH69" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="AI69" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AJ69" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AK69" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL69" t="s" s="2">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="70" hidden="true">
+      <c r="A70" t="s" s="2">
+        <v>409</v>
+      </c>
+      <c r="B70" t="s" s="2">
+        <v>410</v>
+      </c>
+      <c r="C70" s="2"/>
+      <c r="D70" t="s" s="2">
+        <v>188</v>
+      </c>
+      <c r="E70" s="2"/>
+      <c r="F70" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="G70" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="H70" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I70" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J70" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="K70" t="s" s="2">
+        <v>129</v>
+      </c>
+      <c r="L70" t="s" s="2">
+        <v>289</v>
+      </c>
+      <c r="M70" t="s" s="2">
+        <v>290</v>
+      </c>
+      <c r="N70" t="s" s="2">
+        <v>191</v>
+      </c>
+      <c r="O70" s="2"/>
+      <c r="P70" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Q70" s="2"/>
+      <c r="R70" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="S70" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T70" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U70" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V70" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W70" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X70" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y70" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z70" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA70" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB70" t="s" s="2">
+        <v>132</v>
+      </c>
+      <c r="AC70" t="s" s="2">
+        <v>151</v>
+      </c>
+      <c r="AD70" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE70" t="s" s="2">
+        <v>133</v>
+      </c>
+      <c r="AF70" t="s" s="2">
+        <v>152</v>
+      </c>
+      <c r="AG70" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AH70" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AI70" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AJ70" t="s" s="2">
+        <v>135</v>
+      </c>
+      <c r="AK70" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL70" t="s" s="2">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="71" hidden="true">
+      <c r="A71" t="s" s="2">
+        <v>411</v>
+      </c>
+      <c r="B71" t="s" s="2">
+        <v>412</v>
+      </c>
+      <c r="C71" s="2"/>
+      <c r="D71" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="E71" s="2"/>
+      <c r="F71" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="G71" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="H71" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I71" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J71" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="K71" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="L71" t="s" s="2">
+        <v>413</v>
+      </c>
+      <c r="M71" t="s" s="2">
+        <v>414</v>
+      </c>
+      <c r="N71" t="s" s="2">
+        <v>415</v>
+      </c>
+      <c r="O71" t="s" s="2">
+        <v>416</v>
+      </c>
+      <c r="P71" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Q71" s="2"/>
+      <c r="R71" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="S71" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T71" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U71" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V71" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W71" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X71" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y71" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z71" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA71" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB71" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC71" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD71" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE71" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF71" t="s" s="2">
+        <v>417</v>
+      </c>
+      <c r="AG71" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AH71" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="AI71" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AJ71" t="s" s="2">
+        <v>98</v>
+      </c>
+      <c r="AK71" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL71" t="s" s="2">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="72" hidden="true">
+      <c r="A72" t="s" s="2">
+        <v>418</v>
+      </c>
+      <c r="B72" t="s" s="2">
+        <v>419</v>
+      </c>
+      <c r="C72" s="2"/>
+      <c r="D72" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="E72" s="2"/>
+      <c r="F72" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="G72" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="H72" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I72" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J72" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="K72" t="s" s="2">
+        <v>145</v>
+      </c>
+      <c r="L72" t="s" s="2">
+        <v>420</v>
+      </c>
+      <c r="M72" t="s" s="2">
+        <v>421</v>
+      </c>
+      <c r="N72" t="s" s="2">
+        <v>422</v>
+      </c>
+      <c r="O72" s="2"/>
+      <c r="P72" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Q72" s="2"/>
+      <c r="R72" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="S72" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T72" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U72" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V72" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W72" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X72" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y72" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z72" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA72" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB72" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC72" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD72" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE72" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF72" t="s" s="2">
+        <v>423</v>
+      </c>
+      <c r="AG72" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AH72" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="AI72" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AJ72" t="s" s="2">
+        <v>98</v>
+      </c>
+      <c r="AK72" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL72" t="s" s="2">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="73" hidden="true">
+      <c r="A73" t="s" s="2">
+        <v>424</v>
+      </c>
+      <c r="B73" t="s" s="2">
+        <v>425</v>
+      </c>
+      <c r="C73" s="2"/>
+      <c r="D73" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="E73" s="2"/>
+      <c r="F73" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="G73" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="H73" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I73" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J73" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="K73" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="L73" t="s" s="2">
+        <v>426</v>
+      </c>
+      <c r="M73" t="s" s="2">
+        <v>427</v>
+      </c>
+      <c r="N73" s="2"/>
+      <c r="O73" t="s" s="2">
+        <v>428</v>
+      </c>
+      <c r="P73" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Q73" s="2"/>
+      <c r="R73" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="S73" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T73" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U73" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V73" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W73" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X73" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y73" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z73" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA73" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB73" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC73" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD73" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE73" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF73" t="s" s="2">
+        <v>429</v>
+      </c>
+      <c r="AG73" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AH73" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="AI73" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AJ73" t="s" s="2">
+        <v>98</v>
+      </c>
+      <c r="AK73" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL73" t="s" s="2">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="s" s="2">
+        <v>430</v>
+      </c>
+      <c r="B74" t="s" s="2">
+        <v>431</v>
+      </c>
+      <c r="C74" s="2"/>
+      <c r="D74" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="E74" s="2"/>
+      <c r="F74" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="G74" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="H74" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="I74" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J74" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="K74" t="s" s="2">
+        <v>145</v>
+      </c>
+      <c r="L74" t="s" s="2">
+        <v>432</v>
+      </c>
+      <c r="M74" t="s" s="2">
+        <v>433</v>
+      </c>
+      <c r="N74" s="2"/>
+      <c r="O74" t="s" s="2">
+        <v>434</v>
+      </c>
+      <c r="P74" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Q74" s="2"/>
+      <c r="R74" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="S74" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T74" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U74" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V74" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W74" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X74" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y74" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z74" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA74" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB74" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC74" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD74" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE74" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF74" t="s" s="2">
+        <v>435</v>
+      </c>
+      <c r="AG74" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AH74" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="AI74" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AJ74" t="s" s="2">
+        <v>98</v>
+      </c>
+      <c r="AK74" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL74" t="s" s="2">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="75" hidden="true">
+      <c r="A75" t="s" s="2">
+        <v>436</v>
+      </c>
+      <c r="B75" t="s" s="2">
+        <v>437</v>
+      </c>
+      <c r="C75" s="2"/>
+      <c r="D75" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="E75" s="2"/>
+      <c r="F75" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="G75" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="H75" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I75" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J75" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="K75" t="s" s="2">
+        <v>145</v>
+      </c>
+      <c r="L75" t="s" s="2">
+        <v>223</v>
+      </c>
+      <c r="M75" t="s" s="2">
+        <v>224</v>
+      </c>
+      <c r="N75" s="2"/>
+      <c r="O75" s="2"/>
+      <c r="P75" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Q75" s="2"/>
+      <c r="R75" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="S75" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T75" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U75" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V75" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W75" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X75" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y75" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z75" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA75" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB75" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC75" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD75" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE75" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF75" t="s" s="2">
+        <v>148</v>
+      </c>
+      <c r="AG75" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AH75" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="AI75" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AJ75" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AK75" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL75" t="s" s="2">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="76" hidden="true">
+      <c r="A76" t="s" s="2">
+        <v>438</v>
+      </c>
+      <c r="B76" t="s" s="2">
+        <v>439</v>
+      </c>
+      <c r="C76" s="2"/>
+      <c r="D76" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="E76" s="2"/>
+      <c r="F76" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="G76" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="H76" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I76" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J76" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="K76" t="s" s="2">
+        <v>129</v>
+      </c>
+      <c r="L76" t="s" s="2">
+        <v>130</v>
+      </c>
+      <c r="M76" t="s" s="2">
+        <v>131</v>
+      </c>
+      <c r="N76" s="2"/>
+      <c r="O76" s="2"/>
+      <c r="P76" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Q76" s="2"/>
+      <c r="R76" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="S76" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T76" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U76" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V76" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W76" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X76" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y76" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z76" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA76" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB76" t="s" s="2">
+        <v>132</v>
+      </c>
+      <c r="AC76" s="2"/>
+      <c r="AD76" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE76" t="s" s="2">
+        <v>133</v>
+      </c>
+      <c r="AF76" t="s" s="2">
+        <v>152</v>
+      </c>
+      <c r="AG76" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AH76" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AI76" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AJ76" t="s" s="2">
+        <v>135</v>
+      </c>
+      <c r="AK76" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL76" t="s" s="2">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="s" s="2">
+        <v>440</v>
+      </c>
+      <c r="B77" t="s" s="2">
+        <v>439</v>
+      </c>
+      <c r="C77" t="s" s="2">
+        <v>367</v>
+      </c>
+      <c r="D77" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="E77" s="2"/>
+      <c r="F77" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="G77" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="H77" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="I77" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J77" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="K77" t="s" s="2">
+        <v>368</v>
+      </c>
+      <c r="L77" t="s" s="2">
+        <v>369</v>
+      </c>
+      <c r="M77" t="s" s="2">
+        <v>370</v>
+      </c>
+      <c r="N77" s="2"/>
+      <c r="O77" s="2"/>
+      <c r="P77" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Q77" s="2"/>
+      <c r="R77" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="S77" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T77" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U77" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V77" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W77" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X77" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y77" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z77" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA77" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB77" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC77" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD77" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE77" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF77" t="s" s="2">
+        <v>152</v>
+      </c>
+      <c r="AG77" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AH77" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AI77" t="s" s="2">
+        <v>142</v>
+      </c>
+      <c r="AJ77" t="s" s="2">
+        <v>135</v>
+      </c>
+      <c r="AK77" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL77" t="s" s="2">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="78" hidden="true">
+      <c r="A78" t="s" s="2">
+        <v>441</v>
+      </c>
+      <c r="B78" t="s" s="2">
+        <v>442</v>
+      </c>
+      <c r="C78" s="2"/>
+      <c r="D78" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="E78" s="2"/>
+      <c r="F78" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="G78" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="H78" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I78" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J78" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="K78" t="s" s="2">
+        <v>145</v>
+      </c>
+      <c r="L78" t="s" s="2">
+        <v>372</v>
+      </c>
+      <c r="M78" t="s" s="2">
+        <v>373</v>
+      </c>
+      <c r="N78" s="2"/>
+      <c r="O78" s="2"/>
+      <c r="P78" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Q78" s="2"/>
+      <c r="R78" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="S78" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T78" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U78" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V78" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W78" t="s" s="2">
+        <v>374</v>
+      </c>
+      <c r="X78" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y78" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z78" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA78" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB78" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC78" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD78" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE78" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF78" t="s" s="2">
+        <v>375</v>
+      </c>
+      <c r="AG78" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AH78" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="AI78" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AJ78" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AK78" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL78" t="s" s="2">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="79" hidden="true">
+      <c r="A79" t="s" s="2">
+        <v>443</v>
+      </c>
+      <c r="B79" t="s" s="2">
+        <v>444</v>
+      </c>
+      <c r="C79" s="2"/>
+      <c r="D79" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="E79" s="2"/>
+      <c r="F79" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="G79" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="H79" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I79" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J79" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="K79" t="s" s="2">
+        <v>445</v>
+      </c>
+      <c r="L79" t="s" s="2">
+        <v>446</v>
+      </c>
+      <c r="M79" t="s" s="2">
+        <v>447</v>
+      </c>
+      <c r="N79" t="s" s="2">
+        <v>448</v>
+      </c>
+      <c r="O79" t="s" s="2">
+        <v>449</v>
+      </c>
+      <c r="P79" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Q79" s="2"/>
+      <c r="R79" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="S79" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T79" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U79" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V79" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W79" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X79" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y79" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z79" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA79" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB79" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC79" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD79" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE79" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF79" t="s" s="2">
+        <v>450</v>
+      </c>
+      <c r="AG79" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AH79" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="AI79" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AJ79" t="s" s="2">
+        <v>98</v>
+      </c>
+      <c r="AK79" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL79" t="s" s="2">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="s" s="2">
+        <v>451</v>
+      </c>
+      <c r="B80" t="s" s="2">
+        <v>451</v>
+      </c>
+      <c r="C80" s="2"/>
+      <c r="D80" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="E80" s="2"/>
+      <c r="F80" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="G80" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="H80" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="I80" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J80" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="K80" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="L80" t="s" s="2">
+        <v>452</v>
+      </c>
+      <c r="M80" t="s" s="2">
+        <v>453</v>
+      </c>
+      <c r="N80" s="2"/>
+      <c r="O80" t="s" s="2">
+        <v>454</v>
+      </c>
+      <c r="P80" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Q80" s="2"/>
+      <c r="R80" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="S80" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T80" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U80" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V80" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W80" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X80" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y80" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z80" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA80" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB80" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC80" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD80" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE80" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF80" t="s" s="2">
+        <v>451</v>
+      </c>
+      <c r="AG80" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AH80" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AI80" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AJ80" t="s" s="2">
+        <v>98</v>
+      </c>
+      <c r="AK80" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL80" t="s" s="2">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="s" s="2">
+        <v>455</v>
+      </c>
+      <c r="B81" t="s" s="2">
+        <v>455</v>
+      </c>
+      <c r="C81" s="2"/>
+      <c r="D81" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="E81" s="2"/>
+      <c r="F81" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="G81" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="H81" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="I81" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J81" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="K81" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="L81" t="s" s="2">
+        <v>456</v>
+      </c>
+      <c r="M81" t="s" s="2">
+        <v>457</v>
+      </c>
+      <c r="N81" s="2"/>
+      <c r="O81" t="s" s="2">
+        <v>458</v>
+      </c>
+      <c r="P81" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Q81" s="2"/>
+      <c r="R81" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="S81" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T81" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U81" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V81" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W81" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X81" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y81" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z81" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA81" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB81" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC81" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD81" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE81" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF81" t="s" s="2">
+        <v>455</v>
+      </c>
+      <c r="AG81" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AH81" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AI81" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AJ81" t="s" s="2">
+        <v>98</v>
+      </c>
+      <c r="AK81" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL81" t="s" s="2">
         <v>78</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AL65">
+  <autoFilter ref="A1:AL81">
     <filterColumn colId="7">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -8656,7 +10556,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI64">
+  <conditionalFormatting sqref="A2:AI80">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>

--- a/StructureDefinition-mii-pr-pro-questionnaire-response.xlsx
+++ b/StructureDefinition-mii-pr-pro-questionnaire-response.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2027.0.0-ballot.rc5</t>
+    <t>2027.0.0-ballot</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-11T10:35:27+00:00</t>
+    <t>2026-09-11T13:28:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-mii-pr-pro-questionnaire-response.xlsx
+++ b/StructureDefinition-mii-pr-pro-questionnaire-response.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2027.0.0-ballot</t>
+    <t>2027.0.0-ballot.1</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-11T13:28:57+00:00</t>
+    <t>2026-09-11T16:14:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
